--- a/docs/operations/Weez_Beta_Operations.xlsx
+++ b/docs/operations/Weez_Beta_Operations.xlsx
@@ -2,15 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcaa0562312d447a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beta Users" sheetId="2" r:id="R1ff4b085dd34445a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bugs" sheetId="3" r:id="Ra0374170218443c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments" sheetId="4" r:id="R1c9ae197b3a74981"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="5" r:id="R11b6e6a4ceb34f95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="6" r:id="R382c4c2a154641d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Affiliate" sheetId="7" r:id="R4ffd21660b2d4a21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content" sheetId="8" r:id="R82b078855594429f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Ops" sheetId="9" r:id="R8bf4fb729d0145c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf71adaf5977941a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beta Users" sheetId="2" r:id="R06d24a960ff74064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bugs" sheetId="3" r:id="R92eb35eacaf64167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments" sheetId="4" r:id="R3df7e526824748a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="5" r:id="Rb9961f2ec0294642"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="6" r:id="Rd6cc547af5ed4332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Affiliate" sheetId="7" r:id="R37e7ca1a945644e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content" sheetId="8" r:id="Rdcd542ba72a94a24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Ops" sheetId="9" r:id="R1f6e961cf4b9418b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support" sheetId="10" r:id="R6d858af22b6f4ade"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incidents" sheetId="11" r:id="R5d255b2571cd467a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="12" r:id="Rcbae3b992f114a0b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,15 +24,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="&quot;$&quot;#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="203" formatCode="yyyy-mm-dd hh:mm"/>
     <x:numFmt numFmtId="204" formatCode="0.0"/>
     <x:numFmt numFmtId="205" formatCode="0.0%"/>
+    <x:numFmt numFmtId="206" formatCode="$#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="18">
+  <x:fonts count="21">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -128,8 +132,24 @@
       <x:color rgb="FF6D4B00"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF8ED8F8"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1E2935"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -171,8 +191,23 @@
         <x:fgColor rgb="FFFFF4CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17283A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF22394E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="5">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:bottom style="medium">
@@ -197,11 +232,29 @@
         <x:color rgb="FFD8E0E7"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E2EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7E2EA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E2EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7E2EA"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="111">
+  <x:cellXfs count="141">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -453,18 +506,86 @@
     <x:xf numFmtId="205" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="20" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="20" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="20" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="20" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="20" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="20" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="20" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="20" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="20" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="96">
+  <x:dxfs count="100">
     <x:dxf>
       <x:font>
         <x:b/>
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -475,7 +596,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -486,7 +607,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -497,7 +618,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -508,7 +629,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -519,7 +640,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -530,7 +651,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -541,7 +662,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -552,7 +673,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -563,7 +684,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -574,7 +695,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -585,7 +706,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -596,7 +717,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -607,7 +728,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -618,7 +739,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -629,7 +750,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -640,7 +761,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -651,7 +772,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -662,7 +783,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -673,7 +794,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -684,7 +805,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -695,7 +816,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -706,7 +827,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -717,7 +838,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -728,7 +849,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -739,7 +860,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -750,7 +871,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -761,7 +882,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -772,7 +893,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -783,7 +904,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -794,7 +915,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -805,7 +926,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -816,7 +937,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -827,7 +948,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -838,7 +959,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -849,7 +970,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -860,7 +981,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -871,7 +992,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -882,7 +1003,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -893,7 +1014,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -904,7 +1025,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -915,7 +1036,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -926,7 +1047,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -937,7 +1058,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -948,7 +1069,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -959,7 +1080,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -970,7 +1091,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -981,7 +1102,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -992,7 +1113,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1003,7 +1124,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1014,7 +1135,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1025,7 +1146,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1036,7 +1157,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1047,7 +1168,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -1058,7 +1179,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1069,7 +1190,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1080,7 +1201,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1091,7 +1212,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1102,7 +1223,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1113,7 +1234,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -1124,7 +1245,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1135,7 +1256,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1146,7 +1267,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1157,7 +1278,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1168,7 +1289,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1179,7 +1300,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -1190,7 +1311,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1201,7 +1322,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1212,7 +1333,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1223,7 +1344,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1234,7 +1355,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1245,7 +1366,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -1256,7 +1377,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1267,7 +1388,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1278,7 +1399,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1289,7 +1410,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1300,7 +1421,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1311,7 +1432,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -1322,7 +1443,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1333,7 +1454,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1344,7 +1465,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1355,7 +1476,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1366,7 +1487,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1377,7 +1498,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -1388,7 +1509,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1399,7 +1520,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1410,7 +1531,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1421,7 +1542,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1432,7 +1553,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1443,7 +1564,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CF"/>
         </x:patternFill>
       </x:fill>
@@ -1454,7 +1575,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1465,7 +1586,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1476,7 +1597,7 @@
         <x:color rgb="FF137A42"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF6E8"/>
         </x:patternFill>
       </x:fill>
@@ -1487,7 +1608,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1498,7 +1619,7 @@
         <x:color rgb="FFA82222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1509,8 +1630,50 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF0CF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFA71919"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF0CF"/>
+          <x:bgColor rgb="FFFFE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF176B3A"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDFF4E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFA71919"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF176B3A"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDFF4E7"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -1543,6 +1706,42 @@
     <x:tableColumn id="13" name="Rating hands"/>
     <x:tableColumn id="14" name="Last active"/>
     <x:tableColumn id="15" name="Notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="IncidentRegisterTable" displayName="IncidentRegisterTable" ref="A4:N104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="14">
+    <x:tableColumn id="1" name="Opened at"/>
+    <x:tableColumn id="2" name="Incident ID"/>
+    <x:tableColumn id="3" name="Severity"/>
+    <x:tableColumn id="4" name="Surface"/>
+    <x:tableColumn id="5" name="Status"/>
+    <x:tableColumn id="6" name="Owner"/>
+    <x:tableColumn id="7" name="Users affected"/>
+    <x:tableColumn id="8" name="Money affected $"/>
+    <x:tableColumn id="9" name="Detection"/>
+    <x:tableColumn id="10" name="Root cause"/>
+    <x:tableColumn id="11" name="Mitigation"/>
+    <x:tableColumn id="12" name="Resolved at"/>
+    <x:tableColumn id="13" name="Postmortem"/>
+    <x:tableColumn id="14" name="Evidence link"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="MetricDefinitionsTable" displayName="MetricDefinitionsTable" ref="A4:F18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="Metric"/>
+    <x:tableColumn id="2" name="Definition"/>
+    <x:tableColumn id="3" name="Source of truth"/>
+    <x:tableColumn id="4" name="Owner"/>
+    <x:tableColumn id="5" name="Cadence"/>
+    <x:tableColumn id="6" name="Notes"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1710,6 +1909,27 @@
     <x:tableColumn id="13" name="Rating tables"/>
     <x:tableColumn id="14" name="Support backlog"/>
     <x:tableColumn id="15" name="Close notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SupportQueueTable" displayName="SupportQueueTable" ref="A4:M104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="Created at"/>
+    <x:tableColumn id="2" name="Ticket ID"/>
+    <x:tableColumn id="3" name="User"/>
+    <x:tableColumn id="4" name="Channel"/>
+    <x:tableColumn id="5" name="Category"/>
+    <x:tableColumn id="6" name="Priority"/>
+    <x:tableColumn id="7" name="Status"/>
+    <x:tableColumn id="8" name="Owner"/>
+    <x:tableColumn id="9" name="First response"/>
+    <x:tableColumn id="10" name="Resolved at"/>
+    <x:tableColumn id="11" name="SLA hours"/>
+    <x:tableColumn id="12" name="Summary"/>
+    <x:tableColumn id="13" name="Resolution"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1924,7 +2144,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="48" t="str">
-        <x:v>WEEZ · CLOSED BETA CONTROL</x:v>
+        <x:v>WEEZ · OPEN BETA CONTROL</x:v>
       </x:c>
       <x:c r="B1" s="48"/>
       <x:c r="C1" s="48"/>
@@ -1938,7 +2158,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="49" t="str">
-        <x:v>Единый операционный центр. Жёлтые клетки — ручной ввод. Метрики ниже считаются автоматически из остальных вкладок.</x:v>
+        <x:v>Операционный центр открытого теста. Жёлтые клетки — ручной ввод; ключевые метрики считаются автоматически.</x:v>
       </x:c>
       <x:c r="B2" s="49"/>
       <x:c r="C2" s="49"/>
@@ -1990,7 +2210,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="52" t="str">
-        <x:v>Активные тестеры</x:v>
+        <x:v>Активные игроки</x:v>
       </x:c>
       <x:c r="B6" s="52"/>
       <x:c r="C6" s="52" t="str">
@@ -2385,6 +2605,3908 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="34" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="113" t="str">
+        <x:v>Support Queue</x:v>
+      </x:c>
+      <x:c r="B1" s="113"/>
+      <x:c r="C1" s="113"/>
+      <x:c r="D1" s="113"/>
+      <x:c r="E1" s="113"/>
+      <x:c r="F1" s="113"/>
+      <x:c r="G1" s="113"/>
+      <x:c r="H1" s="113"/>
+      <x:c r="I1" s="113"/>
+      <x:c r="J1" s="113"/>
+      <x:c r="K1" s="113"/>
+      <x:c r="L1" s="113"/>
+      <x:c r="M1" s="113"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="116" t="str">
+        <x:v>Один запрос — одна строка. Денежные и P0/P1 обращения эскалируются владельцу сразу.</x:v>
+      </x:c>
+      <x:c r="B2" s="116"/>
+      <x:c r="C2" s="116"/>
+      <x:c r="D2" s="116"/>
+      <x:c r="E2" s="116"/>
+      <x:c r="F2" s="116"/>
+      <x:c r="G2" s="116"/>
+      <x:c r="H2" s="116"/>
+      <x:c r="I2" s="116"/>
+      <x:c r="J2" s="116"/>
+      <x:c r="K2" s="116"/>
+      <x:c r="L2" s="116"/>
+      <x:c r="M2" s="116"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="120" t="str">
+        <x:v>Created at</x:v>
+      </x:c>
+      <x:c r="B4" s="120" t="str">
+        <x:v>Ticket ID</x:v>
+      </x:c>
+      <x:c r="C4" s="120" t="str">
+        <x:v>User</x:v>
+      </x:c>
+      <x:c r="D4" s="120" t="str">
+        <x:v>Channel</x:v>
+      </x:c>
+      <x:c r="E4" s="120" t="str">
+        <x:v>Category</x:v>
+      </x:c>
+      <x:c r="F4" s="120" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="G4" s="120" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H4" s="120" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="I4" s="120" t="str">
+        <x:v>First response</x:v>
+      </x:c>
+      <x:c r="J4" s="120" t="str">
+        <x:v>Resolved at</x:v>
+      </x:c>
+      <x:c r="K4" s="120" t="str">
+        <x:v>SLA hours</x:v>
+      </x:c>
+      <x:c r="L4" s="120" t="str">
+        <x:v>Summary</x:v>
+      </x:c>
+      <x:c r="M4" s="120" t="str">
+        <x:v>Resolution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="129"/>
+      <x:c r="B5" s="126"/>
+      <x:c r="C5" s="126"/>
+      <x:c r="D5" s="126"/>
+      <x:c r="E5" s="126"/>
+      <x:c r="F5" s="126"/>
+      <x:c r="G5" s="126"/>
+      <x:c r="H5" s="126"/>
+      <x:c r="I5" s="129"/>
+      <x:c r="J5" s="129"/>
+      <x:c r="K5" s="132" t="str">
+        <x:f>IF(A5="","",IF(I5="",24*(NOW()-A5),24*(I5-A5)))</x:f>
+      </x:c>
+      <x:c r="L5" s="126"/>
+      <x:c r="M5" s="126"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="130"/>
+      <x:c r="B6" s="127"/>
+      <x:c r="C6" s="127"/>
+      <x:c r="D6" s="127"/>
+      <x:c r="E6" s="127"/>
+      <x:c r="F6" s="127"/>
+      <x:c r="G6" s="127"/>
+      <x:c r="H6" s="127"/>
+      <x:c r="I6" s="130"/>
+      <x:c r="J6" s="130"/>
+      <x:c r="K6" s="133" t="str">
+        <x:f>IF(A6="","",IF(I6="",24*(NOW()-A6),24*(I6-A6)))</x:f>
+      </x:c>
+      <x:c r="L6" s="127"/>
+      <x:c r="M6" s="127"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="130"/>
+      <x:c r="B7" s="127"/>
+      <x:c r="C7" s="127"/>
+      <x:c r="D7" s="127"/>
+      <x:c r="E7" s="127"/>
+      <x:c r="F7" s="127"/>
+      <x:c r="G7" s="127"/>
+      <x:c r="H7" s="127"/>
+      <x:c r="I7" s="130"/>
+      <x:c r="J7" s="130"/>
+      <x:c r="K7" s="133" t="str">
+        <x:f>IF(A7="","",IF(I7="",24*(NOW()-A7),24*(I7-A7)))</x:f>
+      </x:c>
+      <x:c r="L7" s="127"/>
+      <x:c r="M7" s="127"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="130"/>
+      <x:c r="B8" s="127"/>
+      <x:c r="C8" s="127"/>
+      <x:c r="D8" s="127"/>
+      <x:c r="E8" s="127"/>
+      <x:c r="F8" s="127"/>
+      <x:c r="G8" s="127"/>
+      <x:c r="H8" s="127"/>
+      <x:c r="I8" s="130"/>
+      <x:c r="J8" s="130"/>
+      <x:c r="K8" s="133" t="str">
+        <x:f>IF(A8="","",IF(I8="",24*(NOW()-A8),24*(I8-A8)))</x:f>
+      </x:c>
+      <x:c r="L8" s="127"/>
+      <x:c r="M8" s="127"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="130"/>
+      <x:c r="B9" s="127"/>
+      <x:c r="C9" s="127"/>
+      <x:c r="D9" s="127"/>
+      <x:c r="E9" s="127"/>
+      <x:c r="F9" s="127"/>
+      <x:c r="G9" s="127"/>
+      <x:c r="H9" s="127"/>
+      <x:c r="I9" s="130"/>
+      <x:c r="J9" s="130"/>
+      <x:c r="K9" s="133" t="str">
+        <x:f>IF(A9="","",IF(I9="",24*(NOW()-A9),24*(I9-A9)))</x:f>
+      </x:c>
+      <x:c r="L9" s="127"/>
+      <x:c r="M9" s="127"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="130"/>
+      <x:c r="B10" s="127"/>
+      <x:c r="C10" s="127"/>
+      <x:c r="D10" s="127"/>
+      <x:c r="E10" s="127"/>
+      <x:c r="F10" s="127"/>
+      <x:c r="G10" s="127"/>
+      <x:c r="H10" s="127"/>
+      <x:c r="I10" s="130"/>
+      <x:c r="J10" s="130"/>
+      <x:c r="K10" s="133" t="str">
+        <x:f>IF(A10="","",IF(I10="",24*(NOW()-A10),24*(I10-A10)))</x:f>
+      </x:c>
+      <x:c r="L10" s="127"/>
+      <x:c r="M10" s="127"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="130"/>
+      <x:c r="B11" s="127"/>
+      <x:c r="C11" s="127"/>
+      <x:c r="D11" s="127"/>
+      <x:c r="E11" s="127"/>
+      <x:c r="F11" s="127"/>
+      <x:c r="G11" s="127"/>
+      <x:c r="H11" s="127"/>
+      <x:c r="I11" s="130"/>
+      <x:c r="J11" s="130"/>
+      <x:c r="K11" s="133" t="str">
+        <x:f>IF(A11="","",IF(I11="",24*(NOW()-A11),24*(I11-A11)))</x:f>
+      </x:c>
+      <x:c r="L11" s="127"/>
+      <x:c r="M11" s="127"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="130"/>
+      <x:c r="B12" s="127"/>
+      <x:c r="C12" s="127"/>
+      <x:c r="D12" s="127"/>
+      <x:c r="E12" s="127"/>
+      <x:c r="F12" s="127"/>
+      <x:c r="G12" s="127"/>
+      <x:c r="H12" s="127"/>
+      <x:c r="I12" s="130"/>
+      <x:c r="J12" s="130"/>
+      <x:c r="K12" s="133" t="str">
+        <x:f>IF(A12="","",IF(I12="",24*(NOW()-A12),24*(I12-A12)))</x:f>
+      </x:c>
+      <x:c r="L12" s="127"/>
+      <x:c r="M12" s="127"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="130"/>
+      <x:c r="B13" s="127"/>
+      <x:c r="C13" s="127"/>
+      <x:c r="D13" s="127"/>
+      <x:c r="E13" s="127"/>
+      <x:c r="F13" s="127"/>
+      <x:c r="G13" s="127"/>
+      <x:c r="H13" s="127"/>
+      <x:c r="I13" s="130"/>
+      <x:c r="J13" s="130"/>
+      <x:c r="K13" s="133" t="str">
+        <x:f>IF(A13="","",IF(I13="",24*(NOW()-A13),24*(I13-A13)))</x:f>
+      </x:c>
+      <x:c r="L13" s="127"/>
+      <x:c r="M13" s="127"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="130"/>
+      <x:c r="B14" s="127"/>
+      <x:c r="C14" s="127"/>
+      <x:c r="D14" s="127"/>
+      <x:c r="E14" s="127"/>
+      <x:c r="F14" s="127"/>
+      <x:c r="G14" s="127"/>
+      <x:c r="H14" s="127"/>
+      <x:c r="I14" s="130"/>
+      <x:c r="J14" s="130"/>
+      <x:c r="K14" s="133" t="str">
+        <x:f>IF(A14="","",IF(I14="",24*(NOW()-A14),24*(I14-A14)))</x:f>
+      </x:c>
+      <x:c r="L14" s="127"/>
+      <x:c r="M14" s="127"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="130"/>
+      <x:c r="B15" s="127"/>
+      <x:c r="C15" s="127"/>
+      <x:c r="D15" s="127"/>
+      <x:c r="E15" s="127"/>
+      <x:c r="F15" s="127"/>
+      <x:c r="G15" s="127"/>
+      <x:c r="H15" s="127"/>
+      <x:c r="I15" s="130"/>
+      <x:c r="J15" s="130"/>
+      <x:c r="K15" s="133" t="str">
+        <x:f>IF(A15="","",IF(I15="",24*(NOW()-A15),24*(I15-A15)))</x:f>
+      </x:c>
+      <x:c r="L15" s="127"/>
+      <x:c r="M15" s="127"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="130"/>
+      <x:c r="B16" s="127"/>
+      <x:c r="C16" s="127"/>
+      <x:c r="D16" s="127"/>
+      <x:c r="E16" s="127"/>
+      <x:c r="F16" s="127"/>
+      <x:c r="G16" s="127"/>
+      <x:c r="H16" s="127"/>
+      <x:c r="I16" s="130"/>
+      <x:c r="J16" s="130"/>
+      <x:c r="K16" s="133" t="str">
+        <x:f>IF(A16="","",IF(I16="",24*(NOW()-A16),24*(I16-A16)))</x:f>
+      </x:c>
+      <x:c r="L16" s="127"/>
+      <x:c r="M16" s="127"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="130"/>
+      <x:c r="B17" s="127"/>
+      <x:c r="C17" s="127"/>
+      <x:c r="D17" s="127"/>
+      <x:c r="E17" s="127"/>
+      <x:c r="F17" s="127"/>
+      <x:c r="G17" s="127"/>
+      <x:c r="H17" s="127"/>
+      <x:c r="I17" s="130"/>
+      <x:c r="J17" s="130"/>
+      <x:c r="K17" s="133" t="str">
+        <x:f>IF(A17="","",IF(I17="",24*(NOW()-A17),24*(I17-A17)))</x:f>
+      </x:c>
+      <x:c r="L17" s="127"/>
+      <x:c r="M17" s="127"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="130"/>
+      <x:c r="B18" s="127"/>
+      <x:c r="C18" s="127"/>
+      <x:c r="D18" s="127"/>
+      <x:c r="E18" s="127"/>
+      <x:c r="F18" s="127"/>
+      <x:c r="G18" s="127"/>
+      <x:c r="H18" s="127"/>
+      <x:c r="I18" s="130"/>
+      <x:c r="J18" s="130"/>
+      <x:c r="K18" s="133" t="str">
+        <x:f>IF(A18="","",IF(I18="",24*(NOW()-A18),24*(I18-A18)))</x:f>
+      </x:c>
+      <x:c r="L18" s="127"/>
+      <x:c r="M18" s="127"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="130"/>
+      <x:c r="B19" s="127"/>
+      <x:c r="C19" s="127"/>
+      <x:c r="D19" s="127"/>
+      <x:c r="E19" s="127"/>
+      <x:c r="F19" s="127"/>
+      <x:c r="G19" s="127"/>
+      <x:c r="H19" s="127"/>
+      <x:c r="I19" s="130"/>
+      <x:c r="J19" s="130"/>
+      <x:c r="K19" s="133" t="str">
+        <x:f>IF(A19="","",IF(I19="",24*(NOW()-A19),24*(I19-A19)))</x:f>
+      </x:c>
+      <x:c r="L19" s="127"/>
+      <x:c r="M19" s="127"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="130"/>
+      <x:c r="B20" s="127"/>
+      <x:c r="C20" s="127"/>
+      <x:c r="D20" s="127"/>
+      <x:c r="E20" s="127"/>
+      <x:c r="F20" s="127"/>
+      <x:c r="G20" s="127"/>
+      <x:c r="H20" s="127"/>
+      <x:c r="I20" s="130"/>
+      <x:c r="J20" s="130"/>
+      <x:c r="K20" s="133" t="str">
+        <x:f>IF(A20="","",IF(I20="",24*(NOW()-A20),24*(I20-A20)))</x:f>
+      </x:c>
+      <x:c r="L20" s="127"/>
+      <x:c r="M20" s="127"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="130"/>
+      <x:c r="B21" s="127"/>
+      <x:c r="C21" s="127"/>
+      <x:c r="D21" s="127"/>
+      <x:c r="E21" s="127"/>
+      <x:c r="F21" s="127"/>
+      <x:c r="G21" s="127"/>
+      <x:c r="H21" s="127"/>
+      <x:c r="I21" s="130"/>
+      <x:c r="J21" s="130"/>
+      <x:c r="K21" s="133" t="str">
+        <x:f>IF(A21="","",IF(I21="",24*(NOW()-A21),24*(I21-A21)))</x:f>
+      </x:c>
+      <x:c r="L21" s="127"/>
+      <x:c r="M21" s="127"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="130"/>
+      <x:c r="B22" s="127"/>
+      <x:c r="C22" s="127"/>
+      <x:c r="D22" s="127"/>
+      <x:c r="E22" s="127"/>
+      <x:c r="F22" s="127"/>
+      <x:c r="G22" s="127"/>
+      <x:c r="H22" s="127"/>
+      <x:c r="I22" s="130"/>
+      <x:c r="J22" s="130"/>
+      <x:c r="K22" s="133" t="str">
+        <x:f>IF(A22="","",IF(I22="",24*(NOW()-A22),24*(I22-A22)))</x:f>
+      </x:c>
+      <x:c r="L22" s="127"/>
+      <x:c r="M22" s="127"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="130"/>
+      <x:c r="B23" s="127"/>
+      <x:c r="C23" s="127"/>
+      <x:c r="D23" s="127"/>
+      <x:c r="E23" s="127"/>
+      <x:c r="F23" s="127"/>
+      <x:c r="G23" s="127"/>
+      <x:c r="H23" s="127"/>
+      <x:c r="I23" s="130"/>
+      <x:c r="J23" s="130"/>
+      <x:c r="K23" s="133" t="str">
+        <x:f>IF(A23="","",IF(I23="",24*(NOW()-A23),24*(I23-A23)))</x:f>
+      </x:c>
+      <x:c r="L23" s="127"/>
+      <x:c r="M23" s="127"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="130"/>
+      <x:c r="B24" s="127"/>
+      <x:c r="C24" s="127"/>
+      <x:c r="D24" s="127"/>
+      <x:c r="E24" s="127"/>
+      <x:c r="F24" s="127"/>
+      <x:c r="G24" s="127"/>
+      <x:c r="H24" s="127"/>
+      <x:c r="I24" s="130"/>
+      <x:c r="J24" s="130"/>
+      <x:c r="K24" s="133" t="str">
+        <x:f>IF(A24="","",IF(I24="",24*(NOW()-A24),24*(I24-A24)))</x:f>
+      </x:c>
+      <x:c r="L24" s="127"/>
+      <x:c r="M24" s="127"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="130"/>
+      <x:c r="B25" s="127"/>
+      <x:c r="C25" s="127"/>
+      <x:c r="D25" s="127"/>
+      <x:c r="E25" s="127"/>
+      <x:c r="F25" s="127"/>
+      <x:c r="G25" s="127"/>
+      <x:c r="H25" s="127"/>
+      <x:c r="I25" s="130"/>
+      <x:c r="J25" s="130"/>
+      <x:c r="K25" s="133" t="str">
+        <x:f>IF(A25="","",IF(I25="",24*(NOW()-A25),24*(I25-A25)))</x:f>
+      </x:c>
+      <x:c r="L25" s="127"/>
+      <x:c r="M25" s="127"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="130"/>
+      <x:c r="B26" s="127"/>
+      <x:c r="C26" s="127"/>
+      <x:c r="D26" s="127"/>
+      <x:c r="E26" s="127"/>
+      <x:c r="F26" s="127"/>
+      <x:c r="G26" s="127"/>
+      <x:c r="H26" s="127"/>
+      <x:c r="I26" s="130"/>
+      <x:c r="J26" s="130"/>
+      <x:c r="K26" s="133" t="str">
+        <x:f>IF(A26="","",IF(I26="",24*(NOW()-A26),24*(I26-A26)))</x:f>
+      </x:c>
+      <x:c r="L26" s="127"/>
+      <x:c r="M26" s="127"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="130"/>
+      <x:c r="B27" s="127"/>
+      <x:c r="C27" s="127"/>
+      <x:c r="D27" s="127"/>
+      <x:c r="E27" s="127"/>
+      <x:c r="F27" s="127"/>
+      <x:c r="G27" s="127"/>
+      <x:c r="H27" s="127"/>
+      <x:c r="I27" s="130"/>
+      <x:c r="J27" s="130"/>
+      <x:c r="K27" s="133" t="str">
+        <x:f>IF(A27="","",IF(I27="",24*(NOW()-A27),24*(I27-A27)))</x:f>
+      </x:c>
+      <x:c r="L27" s="127"/>
+      <x:c r="M27" s="127"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="130"/>
+      <x:c r="B28" s="127"/>
+      <x:c r="C28" s="127"/>
+      <x:c r="D28" s="127"/>
+      <x:c r="E28" s="127"/>
+      <x:c r="F28" s="127"/>
+      <x:c r="G28" s="127"/>
+      <x:c r="H28" s="127"/>
+      <x:c r="I28" s="130"/>
+      <x:c r="J28" s="130"/>
+      <x:c r="K28" s="133" t="str">
+        <x:f>IF(A28="","",IF(I28="",24*(NOW()-A28),24*(I28-A28)))</x:f>
+      </x:c>
+      <x:c r="L28" s="127"/>
+      <x:c r="M28" s="127"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="130"/>
+      <x:c r="B29" s="127"/>
+      <x:c r="C29" s="127"/>
+      <x:c r="D29" s="127"/>
+      <x:c r="E29" s="127"/>
+      <x:c r="F29" s="127"/>
+      <x:c r="G29" s="127"/>
+      <x:c r="H29" s="127"/>
+      <x:c r="I29" s="130"/>
+      <x:c r="J29" s="130"/>
+      <x:c r="K29" s="133" t="str">
+        <x:f>IF(A29="","",IF(I29="",24*(NOW()-A29),24*(I29-A29)))</x:f>
+      </x:c>
+      <x:c r="L29" s="127"/>
+      <x:c r="M29" s="127"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="130"/>
+      <x:c r="B30" s="127"/>
+      <x:c r="C30" s="127"/>
+      <x:c r="D30" s="127"/>
+      <x:c r="E30" s="127"/>
+      <x:c r="F30" s="127"/>
+      <x:c r="G30" s="127"/>
+      <x:c r="H30" s="127"/>
+      <x:c r="I30" s="130"/>
+      <x:c r="J30" s="130"/>
+      <x:c r="K30" s="133" t="str">
+        <x:f>IF(A30="","",IF(I30="",24*(NOW()-A30),24*(I30-A30)))</x:f>
+      </x:c>
+      <x:c r="L30" s="127"/>
+      <x:c r="M30" s="127"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="130"/>
+      <x:c r="B31" s="127"/>
+      <x:c r="C31" s="127"/>
+      <x:c r="D31" s="127"/>
+      <x:c r="E31" s="127"/>
+      <x:c r="F31" s="127"/>
+      <x:c r="G31" s="127"/>
+      <x:c r="H31" s="127"/>
+      <x:c r="I31" s="130"/>
+      <x:c r="J31" s="130"/>
+      <x:c r="K31" s="133" t="str">
+        <x:f>IF(A31="","",IF(I31="",24*(NOW()-A31),24*(I31-A31)))</x:f>
+      </x:c>
+      <x:c r="L31" s="127"/>
+      <x:c r="M31" s="127"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="130"/>
+      <x:c r="B32" s="127"/>
+      <x:c r="C32" s="127"/>
+      <x:c r="D32" s="127"/>
+      <x:c r="E32" s="127"/>
+      <x:c r="F32" s="127"/>
+      <x:c r="G32" s="127"/>
+      <x:c r="H32" s="127"/>
+      <x:c r="I32" s="130"/>
+      <x:c r="J32" s="130"/>
+      <x:c r="K32" s="133" t="str">
+        <x:f>IF(A32="","",IF(I32="",24*(NOW()-A32),24*(I32-A32)))</x:f>
+      </x:c>
+      <x:c r="L32" s="127"/>
+      <x:c r="M32" s="127"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="130"/>
+      <x:c r="B33" s="127"/>
+      <x:c r="C33" s="127"/>
+      <x:c r="D33" s="127"/>
+      <x:c r="E33" s="127"/>
+      <x:c r="F33" s="127"/>
+      <x:c r="G33" s="127"/>
+      <x:c r="H33" s="127"/>
+      <x:c r="I33" s="130"/>
+      <x:c r="J33" s="130"/>
+      <x:c r="K33" s="133" t="str">
+        <x:f>IF(A33="","",IF(I33="",24*(NOW()-A33),24*(I33-A33)))</x:f>
+      </x:c>
+      <x:c r="L33" s="127"/>
+      <x:c r="M33" s="127"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="130"/>
+      <x:c r="B34" s="127"/>
+      <x:c r="C34" s="127"/>
+      <x:c r="D34" s="127"/>
+      <x:c r="E34" s="127"/>
+      <x:c r="F34" s="127"/>
+      <x:c r="G34" s="127"/>
+      <x:c r="H34" s="127"/>
+      <x:c r="I34" s="130"/>
+      <x:c r="J34" s="130"/>
+      <x:c r="K34" s="133" t="str">
+        <x:f>IF(A34="","",IF(I34="",24*(NOW()-A34),24*(I34-A34)))</x:f>
+      </x:c>
+      <x:c r="L34" s="127"/>
+      <x:c r="M34" s="127"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="130"/>
+      <x:c r="B35" s="127"/>
+      <x:c r="C35" s="127"/>
+      <x:c r="D35" s="127"/>
+      <x:c r="E35" s="127"/>
+      <x:c r="F35" s="127"/>
+      <x:c r="G35" s="127"/>
+      <x:c r="H35" s="127"/>
+      <x:c r="I35" s="130"/>
+      <x:c r="J35" s="130"/>
+      <x:c r="K35" s="133" t="str">
+        <x:f>IF(A35="","",IF(I35="",24*(NOW()-A35),24*(I35-A35)))</x:f>
+      </x:c>
+      <x:c r="L35" s="127"/>
+      <x:c r="M35" s="127"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="130"/>
+      <x:c r="B36" s="127"/>
+      <x:c r="C36" s="127"/>
+      <x:c r="D36" s="127"/>
+      <x:c r="E36" s="127"/>
+      <x:c r="F36" s="127"/>
+      <x:c r="G36" s="127"/>
+      <x:c r="H36" s="127"/>
+      <x:c r="I36" s="130"/>
+      <x:c r="J36" s="130"/>
+      <x:c r="K36" s="133" t="str">
+        <x:f>IF(A36="","",IF(I36="",24*(NOW()-A36),24*(I36-A36)))</x:f>
+      </x:c>
+      <x:c r="L36" s="127"/>
+      <x:c r="M36" s="127"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="130"/>
+      <x:c r="B37" s="127"/>
+      <x:c r="C37" s="127"/>
+      <x:c r="D37" s="127"/>
+      <x:c r="E37" s="127"/>
+      <x:c r="F37" s="127"/>
+      <x:c r="G37" s="127"/>
+      <x:c r="H37" s="127"/>
+      <x:c r="I37" s="130"/>
+      <x:c r="J37" s="130"/>
+      <x:c r="K37" s="133" t="str">
+        <x:f>IF(A37="","",IF(I37="",24*(NOW()-A37),24*(I37-A37)))</x:f>
+      </x:c>
+      <x:c r="L37" s="127"/>
+      <x:c r="M37" s="127"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="130"/>
+      <x:c r="B38" s="127"/>
+      <x:c r="C38" s="127"/>
+      <x:c r="D38" s="127"/>
+      <x:c r="E38" s="127"/>
+      <x:c r="F38" s="127"/>
+      <x:c r="G38" s="127"/>
+      <x:c r="H38" s="127"/>
+      <x:c r="I38" s="130"/>
+      <x:c r="J38" s="130"/>
+      <x:c r="K38" s="133" t="str">
+        <x:f>IF(A38="","",IF(I38="",24*(NOW()-A38),24*(I38-A38)))</x:f>
+      </x:c>
+      <x:c r="L38" s="127"/>
+      <x:c r="M38" s="127"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="130"/>
+      <x:c r="B39" s="127"/>
+      <x:c r="C39" s="127"/>
+      <x:c r="D39" s="127"/>
+      <x:c r="E39" s="127"/>
+      <x:c r="F39" s="127"/>
+      <x:c r="G39" s="127"/>
+      <x:c r="H39" s="127"/>
+      <x:c r="I39" s="130"/>
+      <x:c r="J39" s="130"/>
+      <x:c r="K39" s="133" t="str">
+        <x:f>IF(A39="","",IF(I39="",24*(NOW()-A39),24*(I39-A39)))</x:f>
+      </x:c>
+      <x:c r="L39" s="127"/>
+      <x:c r="M39" s="127"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="130"/>
+      <x:c r="B40" s="127"/>
+      <x:c r="C40" s="127"/>
+      <x:c r="D40" s="127"/>
+      <x:c r="E40" s="127"/>
+      <x:c r="F40" s="127"/>
+      <x:c r="G40" s="127"/>
+      <x:c r="H40" s="127"/>
+      <x:c r="I40" s="130"/>
+      <x:c r="J40" s="130"/>
+      <x:c r="K40" s="133" t="str">
+        <x:f>IF(A40="","",IF(I40="",24*(NOW()-A40),24*(I40-A40)))</x:f>
+      </x:c>
+      <x:c r="L40" s="127"/>
+      <x:c r="M40" s="127"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="130"/>
+      <x:c r="B41" s="127"/>
+      <x:c r="C41" s="127"/>
+      <x:c r="D41" s="127"/>
+      <x:c r="E41" s="127"/>
+      <x:c r="F41" s="127"/>
+      <x:c r="G41" s="127"/>
+      <x:c r="H41" s="127"/>
+      <x:c r="I41" s="130"/>
+      <x:c r="J41" s="130"/>
+      <x:c r="K41" s="133" t="str">
+        <x:f>IF(A41="","",IF(I41="",24*(NOW()-A41),24*(I41-A41)))</x:f>
+      </x:c>
+      <x:c r="L41" s="127"/>
+      <x:c r="M41" s="127"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="130"/>
+      <x:c r="B42" s="127"/>
+      <x:c r="C42" s="127"/>
+      <x:c r="D42" s="127"/>
+      <x:c r="E42" s="127"/>
+      <x:c r="F42" s="127"/>
+      <x:c r="G42" s="127"/>
+      <x:c r="H42" s="127"/>
+      <x:c r="I42" s="130"/>
+      <x:c r="J42" s="130"/>
+      <x:c r="K42" s="133" t="str">
+        <x:f>IF(A42="","",IF(I42="",24*(NOW()-A42),24*(I42-A42)))</x:f>
+      </x:c>
+      <x:c r="L42" s="127"/>
+      <x:c r="M42" s="127"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="130"/>
+      <x:c r="B43" s="127"/>
+      <x:c r="C43" s="127"/>
+      <x:c r="D43" s="127"/>
+      <x:c r="E43" s="127"/>
+      <x:c r="F43" s="127"/>
+      <x:c r="G43" s="127"/>
+      <x:c r="H43" s="127"/>
+      <x:c r="I43" s="130"/>
+      <x:c r="J43" s="130"/>
+      <x:c r="K43" s="133" t="str">
+        <x:f>IF(A43="","",IF(I43="",24*(NOW()-A43),24*(I43-A43)))</x:f>
+      </x:c>
+      <x:c r="L43" s="127"/>
+      <x:c r="M43" s="127"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="130"/>
+      <x:c r="B44" s="127"/>
+      <x:c r="C44" s="127"/>
+      <x:c r="D44" s="127"/>
+      <x:c r="E44" s="127"/>
+      <x:c r="F44" s="127"/>
+      <x:c r="G44" s="127"/>
+      <x:c r="H44" s="127"/>
+      <x:c r="I44" s="130"/>
+      <x:c r="J44" s="130"/>
+      <x:c r="K44" s="133" t="str">
+        <x:f>IF(A44="","",IF(I44="",24*(NOW()-A44),24*(I44-A44)))</x:f>
+      </x:c>
+      <x:c r="L44" s="127"/>
+      <x:c r="M44" s="127"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="130"/>
+      <x:c r="B45" s="127"/>
+      <x:c r="C45" s="127"/>
+      <x:c r="D45" s="127"/>
+      <x:c r="E45" s="127"/>
+      <x:c r="F45" s="127"/>
+      <x:c r="G45" s="127"/>
+      <x:c r="H45" s="127"/>
+      <x:c r="I45" s="130"/>
+      <x:c r="J45" s="130"/>
+      <x:c r="K45" s="133" t="str">
+        <x:f>IF(A45="","",IF(I45="",24*(NOW()-A45),24*(I45-A45)))</x:f>
+      </x:c>
+      <x:c r="L45" s="127"/>
+      <x:c r="M45" s="127"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="130"/>
+      <x:c r="B46" s="127"/>
+      <x:c r="C46" s="127"/>
+      <x:c r="D46" s="127"/>
+      <x:c r="E46" s="127"/>
+      <x:c r="F46" s="127"/>
+      <x:c r="G46" s="127"/>
+      <x:c r="H46" s="127"/>
+      <x:c r="I46" s="130"/>
+      <x:c r="J46" s="130"/>
+      <x:c r="K46" s="133" t="str">
+        <x:f>IF(A46="","",IF(I46="",24*(NOW()-A46),24*(I46-A46)))</x:f>
+      </x:c>
+      <x:c r="L46" s="127"/>
+      <x:c r="M46" s="127"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="130"/>
+      <x:c r="B47" s="127"/>
+      <x:c r="C47" s="127"/>
+      <x:c r="D47" s="127"/>
+      <x:c r="E47" s="127"/>
+      <x:c r="F47" s="127"/>
+      <x:c r="G47" s="127"/>
+      <x:c r="H47" s="127"/>
+      <x:c r="I47" s="130"/>
+      <x:c r="J47" s="130"/>
+      <x:c r="K47" s="133" t="str">
+        <x:f>IF(A47="","",IF(I47="",24*(NOW()-A47),24*(I47-A47)))</x:f>
+      </x:c>
+      <x:c r="L47" s="127"/>
+      <x:c r="M47" s="127"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="130"/>
+      <x:c r="B48" s="127"/>
+      <x:c r="C48" s="127"/>
+      <x:c r="D48" s="127"/>
+      <x:c r="E48" s="127"/>
+      <x:c r="F48" s="127"/>
+      <x:c r="G48" s="127"/>
+      <x:c r="H48" s="127"/>
+      <x:c r="I48" s="130"/>
+      <x:c r="J48" s="130"/>
+      <x:c r="K48" s="133" t="str">
+        <x:f>IF(A48="","",IF(I48="",24*(NOW()-A48),24*(I48-A48)))</x:f>
+      </x:c>
+      <x:c r="L48" s="127"/>
+      <x:c r="M48" s="127"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="130"/>
+      <x:c r="B49" s="127"/>
+      <x:c r="C49" s="127"/>
+      <x:c r="D49" s="127"/>
+      <x:c r="E49" s="127"/>
+      <x:c r="F49" s="127"/>
+      <x:c r="G49" s="127"/>
+      <x:c r="H49" s="127"/>
+      <x:c r="I49" s="130"/>
+      <x:c r="J49" s="130"/>
+      <x:c r="K49" s="133" t="str">
+        <x:f>IF(A49="","",IF(I49="",24*(NOW()-A49),24*(I49-A49)))</x:f>
+      </x:c>
+      <x:c r="L49" s="127"/>
+      <x:c r="M49" s="127"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="130"/>
+      <x:c r="B50" s="127"/>
+      <x:c r="C50" s="127"/>
+      <x:c r="D50" s="127"/>
+      <x:c r="E50" s="127"/>
+      <x:c r="F50" s="127"/>
+      <x:c r="G50" s="127"/>
+      <x:c r="H50" s="127"/>
+      <x:c r="I50" s="130"/>
+      <x:c r="J50" s="130"/>
+      <x:c r="K50" s="133" t="str">
+        <x:f>IF(A50="","",IF(I50="",24*(NOW()-A50),24*(I50-A50)))</x:f>
+      </x:c>
+      <x:c r="L50" s="127"/>
+      <x:c r="M50" s="127"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="130"/>
+      <x:c r="B51" s="127"/>
+      <x:c r="C51" s="127"/>
+      <x:c r="D51" s="127"/>
+      <x:c r="E51" s="127"/>
+      <x:c r="F51" s="127"/>
+      <x:c r="G51" s="127"/>
+      <x:c r="H51" s="127"/>
+      <x:c r="I51" s="130"/>
+      <x:c r="J51" s="130"/>
+      <x:c r="K51" s="133" t="str">
+        <x:f>IF(A51="","",IF(I51="",24*(NOW()-A51),24*(I51-A51)))</x:f>
+      </x:c>
+      <x:c r="L51" s="127"/>
+      <x:c r="M51" s="127"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="130"/>
+      <x:c r="B52" s="127"/>
+      <x:c r="C52" s="127"/>
+      <x:c r="D52" s="127"/>
+      <x:c r="E52" s="127"/>
+      <x:c r="F52" s="127"/>
+      <x:c r="G52" s="127"/>
+      <x:c r="H52" s="127"/>
+      <x:c r="I52" s="130"/>
+      <x:c r="J52" s="130"/>
+      <x:c r="K52" s="133" t="str">
+        <x:f>IF(A52="","",IF(I52="",24*(NOW()-A52),24*(I52-A52)))</x:f>
+      </x:c>
+      <x:c r="L52" s="127"/>
+      <x:c r="M52" s="127"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="130"/>
+      <x:c r="B53" s="127"/>
+      <x:c r="C53" s="127"/>
+      <x:c r="D53" s="127"/>
+      <x:c r="E53" s="127"/>
+      <x:c r="F53" s="127"/>
+      <x:c r="G53" s="127"/>
+      <x:c r="H53" s="127"/>
+      <x:c r="I53" s="130"/>
+      <x:c r="J53" s="130"/>
+      <x:c r="K53" s="133" t="str">
+        <x:f>IF(A53="","",IF(I53="",24*(NOW()-A53),24*(I53-A53)))</x:f>
+      </x:c>
+      <x:c r="L53" s="127"/>
+      <x:c r="M53" s="127"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="130"/>
+      <x:c r="B54" s="127"/>
+      <x:c r="C54" s="127"/>
+      <x:c r="D54" s="127"/>
+      <x:c r="E54" s="127"/>
+      <x:c r="F54" s="127"/>
+      <x:c r="G54" s="127"/>
+      <x:c r="H54" s="127"/>
+      <x:c r="I54" s="130"/>
+      <x:c r="J54" s="130"/>
+      <x:c r="K54" s="133" t="str">
+        <x:f>IF(A54="","",IF(I54="",24*(NOW()-A54),24*(I54-A54)))</x:f>
+      </x:c>
+      <x:c r="L54" s="127"/>
+      <x:c r="M54" s="127"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="130"/>
+      <x:c r="B55" s="127"/>
+      <x:c r="C55" s="127"/>
+      <x:c r="D55" s="127"/>
+      <x:c r="E55" s="127"/>
+      <x:c r="F55" s="127"/>
+      <x:c r="G55" s="127"/>
+      <x:c r="H55" s="127"/>
+      <x:c r="I55" s="130"/>
+      <x:c r="J55" s="130"/>
+      <x:c r="K55" s="133" t="str">
+        <x:f>IF(A55="","",IF(I55="",24*(NOW()-A55),24*(I55-A55)))</x:f>
+      </x:c>
+      <x:c r="L55" s="127"/>
+      <x:c r="M55" s="127"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="130"/>
+      <x:c r="B56" s="127"/>
+      <x:c r="C56" s="127"/>
+      <x:c r="D56" s="127"/>
+      <x:c r="E56" s="127"/>
+      <x:c r="F56" s="127"/>
+      <x:c r="G56" s="127"/>
+      <x:c r="H56" s="127"/>
+      <x:c r="I56" s="130"/>
+      <x:c r="J56" s="130"/>
+      <x:c r="K56" s="133" t="str">
+        <x:f>IF(A56="","",IF(I56="",24*(NOW()-A56),24*(I56-A56)))</x:f>
+      </x:c>
+      <x:c r="L56" s="127"/>
+      <x:c r="M56" s="127"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="130"/>
+      <x:c r="B57" s="127"/>
+      <x:c r="C57" s="127"/>
+      <x:c r="D57" s="127"/>
+      <x:c r="E57" s="127"/>
+      <x:c r="F57" s="127"/>
+      <x:c r="G57" s="127"/>
+      <x:c r="H57" s="127"/>
+      <x:c r="I57" s="130"/>
+      <x:c r="J57" s="130"/>
+      <x:c r="K57" s="133" t="str">
+        <x:f>IF(A57="","",IF(I57="",24*(NOW()-A57),24*(I57-A57)))</x:f>
+      </x:c>
+      <x:c r="L57" s="127"/>
+      <x:c r="M57" s="127"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="130"/>
+      <x:c r="B58" s="127"/>
+      <x:c r="C58" s="127"/>
+      <x:c r="D58" s="127"/>
+      <x:c r="E58" s="127"/>
+      <x:c r="F58" s="127"/>
+      <x:c r="G58" s="127"/>
+      <x:c r="H58" s="127"/>
+      <x:c r="I58" s="130"/>
+      <x:c r="J58" s="130"/>
+      <x:c r="K58" s="133" t="str">
+        <x:f>IF(A58="","",IF(I58="",24*(NOW()-A58),24*(I58-A58)))</x:f>
+      </x:c>
+      <x:c r="L58" s="127"/>
+      <x:c r="M58" s="127"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="130"/>
+      <x:c r="B59" s="127"/>
+      <x:c r="C59" s="127"/>
+      <x:c r="D59" s="127"/>
+      <x:c r="E59" s="127"/>
+      <x:c r="F59" s="127"/>
+      <x:c r="G59" s="127"/>
+      <x:c r="H59" s="127"/>
+      <x:c r="I59" s="130"/>
+      <x:c r="J59" s="130"/>
+      <x:c r="K59" s="133" t="str">
+        <x:f>IF(A59="","",IF(I59="",24*(NOW()-A59),24*(I59-A59)))</x:f>
+      </x:c>
+      <x:c r="L59" s="127"/>
+      <x:c r="M59" s="127"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="130"/>
+      <x:c r="B60" s="127"/>
+      <x:c r="C60" s="127"/>
+      <x:c r="D60" s="127"/>
+      <x:c r="E60" s="127"/>
+      <x:c r="F60" s="127"/>
+      <x:c r="G60" s="127"/>
+      <x:c r="H60" s="127"/>
+      <x:c r="I60" s="130"/>
+      <x:c r="J60" s="130"/>
+      <x:c r="K60" s="133" t="str">
+        <x:f>IF(A60="","",IF(I60="",24*(NOW()-A60),24*(I60-A60)))</x:f>
+      </x:c>
+      <x:c r="L60" s="127"/>
+      <x:c r="M60" s="127"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="130"/>
+      <x:c r="B61" s="127"/>
+      <x:c r="C61" s="127"/>
+      <x:c r="D61" s="127"/>
+      <x:c r="E61" s="127"/>
+      <x:c r="F61" s="127"/>
+      <x:c r="G61" s="127"/>
+      <x:c r="H61" s="127"/>
+      <x:c r="I61" s="130"/>
+      <x:c r="J61" s="130"/>
+      <x:c r="K61" s="133" t="str">
+        <x:f>IF(A61="","",IF(I61="",24*(NOW()-A61),24*(I61-A61)))</x:f>
+      </x:c>
+      <x:c r="L61" s="127"/>
+      <x:c r="M61" s="127"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="130"/>
+      <x:c r="B62" s="127"/>
+      <x:c r="C62" s="127"/>
+      <x:c r="D62" s="127"/>
+      <x:c r="E62" s="127"/>
+      <x:c r="F62" s="127"/>
+      <x:c r="G62" s="127"/>
+      <x:c r="H62" s="127"/>
+      <x:c r="I62" s="130"/>
+      <x:c r="J62" s="130"/>
+      <x:c r="K62" s="133" t="str">
+        <x:f>IF(A62="","",IF(I62="",24*(NOW()-A62),24*(I62-A62)))</x:f>
+      </x:c>
+      <x:c r="L62" s="127"/>
+      <x:c r="M62" s="127"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="130"/>
+      <x:c r="B63" s="127"/>
+      <x:c r="C63" s="127"/>
+      <x:c r="D63" s="127"/>
+      <x:c r="E63" s="127"/>
+      <x:c r="F63" s="127"/>
+      <x:c r="G63" s="127"/>
+      <x:c r="H63" s="127"/>
+      <x:c r="I63" s="130"/>
+      <x:c r="J63" s="130"/>
+      <x:c r="K63" s="133" t="str">
+        <x:f>IF(A63="","",IF(I63="",24*(NOW()-A63),24*(I63-A63)))</x:f>
+      </x:c>
+      <x:c r="L63" s="127"/>
+      <x:c r="M63" s="127"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="130"/>
+      <x:c r="B64" s="127"/>
+      <x:c r="C64" s="127"/>
+      <x:c r="D64" s="127"/>
+      <x:c r="E64" s="127"/>
+      <x:c r="F64" s="127"/>
+      <x:c r="G64" s="127"/>
+      <x:c r="H64" s="127"/>
+      <x:c r="I64" s="130"/>
+      <x:c r="J64" s="130"/>
+      <x:c r="K64" s="133" t="str">
+        <x:f>IF(A64="","",IF(I64="",24*(NOW()-A64),24*(I64-A64)))</x:f>
+      </x:c>
+      <x:c r="L64" s="127"/>
+      <x:c r="M64" s="127"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="130"/>
+      <x:c r="B65" s="127"/>
+      <x:c r="C65" s="127"/>
+      <x:c r="D65" s="127"/>
+      <x:c r="E65" s="127"/>
+      <x:c r="F65" s="127"/>
+      <x:c r="G65" s="127"/>
+      <x:c r="H65" s="127"/>
+      <x:c r="I65" s="130"/>
+      <x:c r="J65" s="130"/>
+      <x:c r="K65" s="133" t="str">
+        <x:f>IF(A65="","",IF(I65="",24*(NOW()-A65),24*(I65-A65)))</x:f>
+      </x:c>
+      <x:c r="L65" s="127"/>
+      <x:c r="M65" s="127"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="130"/>
+      <x:c r="B66" s="127"/>
+      <x:c r="C66" s="127"/>
+      <x:c r="D66" s="127"/>
+      <x:c r="E66" s="127"/>
+      <x:c r="F66" s="127"/>
+      <x:c r="G66" s="127"/>
+      <x:c r="H66" s="127"/>
+      <x:c r="I66" s="130"/>
+      <x:c r="J66" s="130"/>
+      <x:c r="K66" s="133" t="str">
+        <x:f>IF(A66="","",IF(I66="",24*(NOW()-A66),24*(I66-A66)))</x:f>
+      </x:c>
+      <x:c r="L66" s="127"/>
+      <x:c r="M66" s="127"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="130"/>
+      <x:c r="B67" s="127"/>
+      <x:c r="C67" s="127"/>
+      <x:c r="D67" s="127"/>
+      <x:c r="E67" s="127"/>
+      <x:c r="F67" s="127"/>
+      <x:c r="G67" s="127"/>
+      <x:c r="H67" s="127"/>
+      <x:c r="I67" s="130"/>
+      <x:c r="J67" s="130"/>
+      <x:c r="K67" s="133" t="str">
+        <x:f>IF(A67="","",IF(I67="",24*(NOW()-A67),24*(I67-A67)))</x:f>
+      </x:c>
+      <x:c r="L67" s="127"/>
+      <x:c r="M67" s="127"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="130"/>
+      <x:c r="B68" s="127"/>
+      <x:c r="C68" s="127"/>
+      <x:c r="D68" s="127"/>
+      <x:c r="E68" s="127"/>
+      <x:c r="F68" s="127"/>
+      <x:c r="G68" s="127"/>
+      <x:c r="H68" s="127"/>
+      <x:c r="I68" s="130"/>
+      <x:c r="J68" s="130"/>
+      <x:c r="K68" s="133" t="str">
+        <x:f>IF(A68="","",IF(I68="",24*(NOW()-A68),24*(I68-A68)))</x:f>
+      </x:c>
+      <x:c r="L68" s="127"/>
+      <x:c r="M68" s="127"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="130"/>
+      <x:c r="B69" s="127"/>
+      <x:c r="C69" s="127"/>
+      <x:c r="D69" s="127"/>
+      <x:c r="E69" s="127"/>
+      <x:c r="F69" s="127"/>
+      <x:c r="G69" s="127"/>
+      <x:c r="H69" s="127"/>
+      <x:c r="I69" s="130"/>
+      <x:c r="J69" s="130"/>
+      <x:c r="K69" s="133" t="str">
+        <x:f>IF(A69="","",IF(I69="",24*(NOW()-A69),24*(I69-A69)))</x:f>
+      </x:c>
+      <x:c r="L69" s="127"/>
+      <x:c r="M69" s="127"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="130"/>
+      <x:c r="B70" s="127"/>
+      <x:c r="C70" s="127"/>
+      <x:c r="D70" s="127"/>
+      <x:c r="E70" s="127"/>
+      <x:c r="F70" s="127"/>
+      <x:c r="G70" s="127"/>
+      <x:c r="H70" s="127"/>
+      <x:c r="I70" s="130"/>
+      <x:c r="J70" s="130"/>
+      <x:c r="K70" s="133" t="str">
+        <x:f>IF(A70="","",IF(I70="",24*(NOW()-A70),24*(I70-A70)))</x:f>
+      </x:c>
+      <x:c r="L70" s="127"/>
+      <x:c r="M70" s="127"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="130"/>
+      <x:c r="B71" s="127"/>
+      <x:c r="C71" s="127"/>
+      <x:c r="D71" s="127"/>
+      <x:c r="E71" s="127"/>
+      <x:c r="F71" s="127"/>
+      <x:c r="G71" s="127"/>
+      <x:c r="H71" s="127"/>
+      <x:c r="I71" s="130"/>
+      <x:c r="J71" s="130"/>
+      <x:c r="K71" s="133" t="str">
+        <x:f>IF(A71="","",IF(I71="",24*(NOW()-A71),24*(I71-A71)))</x:f>
+      </x:c>
+      <x:c r="L71" s="127"/>
+      <x:c r="M71" s="127"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="130"/>
+      <x:c r="B72" s="127"/>
+      <x:c r="C72" s="127"/>
+      <x:c r="D72" s="127"/>
+      <x:c r="E72" s="127"/>
+      <x:c r="F72" s="127"/>
+      <x:c r="G72" s="127"/>
+      <x:c r="H72" s="127"/>
+      <x:c r="I72" s="130"/>
+      <x:c r="J72" s="130"/>
+      <x:c r="K72" s="133" t="str">
+        <x:f>IF(A72="","",IF(I72="",24*(NOW()-A72),24*(I72-A72)))</x:f>
+      </x:c>
+      <x:c r="L72" s="127"/>
+      <x:c r="M72" s="127"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="130"/>
+      <x:c r="B73" s="127"/>
+      <x:c r="C73" s="127"/>
+      <x:c r="D73" s="127"/>
+      <x:c r="E73" s="127"/>
+      <x:c r="F73" s="127"/>
+      <x:c r="G73" s="127"/>
+      <x:c r="H73" s="127"/>
+      <x:c r="I73" s="130"/>
+      <x:c r="J73" s="130"/>
+      <x:c r="K73" s="133" t="str">
+        <x:f>IF(A73="","",IF(I73="",24*(NOW()-A73),24*(I73-A73)))</x:f>
+      </x:c>
+      <x:c r="L73" s="127"/>
+      <x:c r="M73" s="127"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="130"/>
+      <x:c r="B74" s="127"/>
+      <x:c r="C74" s="127"/>
+      <x:c r="D74" s="127"/>
+      <x:c r="E74" s="127"/>
+      <x:c r="F74" s="127"/>
+      <x:c r="G74" s="127"/>
+      <x:c r="H74" s="127"/>
+      <x:c r="I74" s="130"/>
+      <x:c r="J74" s="130"/>
+      <x:c r="K74" s="133" t="str">
+        <x:f>IF(A74="","",IF(I74="",24*(NOW()-A74),24*(I74-A74)))</x:f>
+      </x:c>
+      <x:c r="L74" s="127"/>
+      <x:c r="M74" s="127"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="130"/>
+      <x:c r="B75" s="127"/>
+      <x:c r="C75" s="127"/>
+      <x:c r="D75" s="127"/>
+      <x:c r="E75" s="127"/>
+      <x:c r="F75" s="127"/>
+      <x:c r="G75" s="127"/>
+      <x:c r="H75" s="127"/>
+      <x:c r="I75" s="130"/>
+      <x:c r="J75" s="130"/>
+      <x:c r="K75" s="133" t="str">
+        <x:f>IF(A75="","",IF(I75="",24*(NOW()-A75),24*(I75-A75)))</x:f>
+      </x:c>
+      <x:c r="L75" s="127"/>
+      <x:c r="M75" s="127"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="130"/>
+      <x:c r="B76" s="127"/>
+      <x:c r="C76" s="127"/>
+      <x:c r="D76" s="127"/>
+      <x:c r="E76" s="127"/>
+      <x:c r="F76" s="127"/>
+      <x:c r="G76" s="127"/>
+      <x:c r="H76" s="127"/>
+      <x:c r="I76" s="130"/>
+      <x:c r="J76" s="130"/>
+      <x:c r="K76" s="133" t="str">
+        <x:f>IF(A76="","",IF(I76="",24*(NOW()-A76),24*(I76-A76)))</x:f>
+      </x:c>
+      <x:c r="L76" s="127"/>
+      <x:c r="M76" s="127"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="130"/>
+      <x:c r="B77" s="127"/>
+      <x:c r="C77" s="127"/>
+      <x:c r="D77" s="127"/>
+      <x:c r="E77" s="127"/>
+      <x:c r="F77" s="127"/>
+      <x:c r="G77" s="127"/>
+      <x:c r="H77" s="127"/>
+      <x:c r="I77" s="130"/>
+      <x:c r="J77" s="130"/>
+      <x:c r="K77" s="133" t="str">
+        <x:f>IF(A77="","",IF(I77="",24*(NOW()-A77),24*(I77-A77)))</x:f>
+      </x:c>
+      <x:c r="L77" s="127"/>
+      <x:c r="M77" s="127"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="130"/>
+      <x:c r="B78" s="127"/>
+      <x:c r="C78" s="127"/>
+      <x:c r="D78" s="127"/>
+      <x:c r="E78" s="127"/>
+      <x:c r="F78" s="127"/>
+      <x:c r="G78" s="127"/>
+      <x:c r="H78" s="127"/>
+      <x:c r="I78" s="130"/>
+      <x:c r="J78" s="130"/>
+      <x:c r="K78" s="133" t="str">
+        <x:f>IF(A78="","",IF(I78="",24*(NOW()-A78),24*(I78-A78)))</x:f>
+      </x:c>
+      <x:c r="L78" s="127"/>
+      <x:c r="M78" s="127"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="130"/>
+      <x:c r="B79" s="127"/>
+      <x:c r="C79" s="127"/>
+      <x:c r="D79" s="127"/>
+      <x:c r="E79" s="127"/>
+      <x:c r="F79" s="127"/>
+      <x:c r="G79" s="127"/>
+      <x:c r="H79" s="127"/>
+      <x:c r="I79" s="130"/>
+      <x:c r="J79" s="130"/>
+      <x:c r="K79" s="133" t="str">
+        <x:f>IF(A79="","",IF(I79="",24*(NOW()-A79),24*(I79-A79)))</x:f>
+      </x:c>
+      <x:c r="L79" s="127"/>
+      <x:c r="M79" s="127"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="130"/>
+      <x:c r="B80" s="127"/>
+      <x:c r="C80" s="127"/>
+      <x:c r="D80" s="127"/>
+      <x:c r="E80" s="127"/>
+      <x:c r="F80" s="127"/>
+      <x:c r="G80" s="127"/>
+      <x:c r="H80" s="127"/>
+      <x:c r="I80" s="130"/>
+      <x:c r="J80" s="130"/>
+      <x:c r="K80" s="133" t="str">
+        <x:f>IF(A80="","",IF(I80="",24*(NOW()-A80),24*(I80-A80)))</x:f>
+      </x:c>
+      <x:c r="L80" s="127"/>
+      <x:c r="M80" s="127"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="130"/>
+      <x:c r="B81" s="127"/>
+      <x:c r="C81" s="127"/>
+      <x:c r="D81" s="127"/>
+      <x:c r="E81" s="127"/>
+      <x:c r="F81" s="127"/>
+      <x:c r="G81" s="127"/>
+      <x:c r="H81" s="127"/>
+      <x:c r="I81" s="130"/>
+      <x:c r="J81" s="130"/>
+      <x:c r="K81" s="133" t="str">
+        <x:f>IF(A81="","",IF(I81="",24*(NOW()-A81),24*(I81-A81)))</x:f>
+      </x:c>
+      <x:c r="L81" s="127"/>
+      <x:c r="M81" s="127"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="130"/>
+      <x:c r="B82" s="127"/>
+      <x:c r="C82" s="127"/>
+      <x:c r="D82" s="127"/>
+      <x:c r="E82" s="127"/>
+      <x:c r="F82" s="127"/>
+      <x:c r="G82" s="127"/>
+      <x:c r="H82" s="127"/>
+      <x:c r="I82" s="130"/>
+      <x:c r="J82" s="130"/>
+      <x:c r="K82" s="133" t="str">
+        <x:f>IF(A82="","",IF(I82="",24*(NOW()-A82),24*(I82-A82)))</x:f>
+      </x:c>
+      <x:c r="L82" s="127"/>
+      <x:c r="M82" s="127"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="130"/>
+      <x:c r="B83" s="127"/>
+      <x:c r="C83" s="127"/>
+      <x:c r="D83" s="127"/>
+      <x:c r="E83" s="127"/>
+      <x:c r="F83" s="127"/>
+      <x:c r="G83" s="127"/>
+      <x:c r="H83" s="127"/>
+      <x:c r="I83" s="130"/>
+      <x:c r="J83" s="130"/>
+      <x:c r="K83" s="133" t="str">
+        <x:f>IF(A83="","",IF(I83="",24*(NOW()-A83),24*(I83-A83)))</x:f>
+      </x:c>
+      <x:c r="L83" s="127"/>
+      <x:c r="M83" s="127"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="130"/>
+      <x:c r="B84" s="127"/>
+      <x:c r="C84" s="127"/>
+      <x:c r="D84" s="127"/>
+      <x:c r="E84" s="127"/>
+      <x:c r="F84" s="127"/>
+      <x:c r="G84" s="127"/>
+      <x:c r="H84" s="127"/>
+      <x:c r="I84" s="130"/>
+      <x:c r="J84" s="130"/>
+      <x:c r="K84" s="133" t="str">
+        <x:f>IF(A84="","",IF(I84="",24*(NOW()-A84),24*(I84-A84)))</x:f>
+      </x:c>
+      <x:c r="L84" s="127"/>
+      <x:c r="M84" s="127"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="130"/>
+      <x:c r="B85" s="127"/>
+      <x:c r="C85" s="127"/>
+      <x:c r="D85" s="127"/>
+      <x:c r="E85" s="127"/>
+      <x:c r="F85" s="127"/>
+      <x:c r="G85" s="127"/>
+      <x:c r="H85" s="127"/>
+      <x:c r="I85" s="130"/>
+      <x:c r="J85" s="130"/>
+      <x:c r="K85" s="133" t="str">
+        <x:f>IF(A85="","",IF(I85="",24*(NOW()-A85),24*(I85-A85)))</x:f>
+      </x:c>
+      <x:c r="L85" s="127"/>
+      <x:c r="M85" s="127"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="130"/>
+      <x:c r="B86" s="127"/>
+      <x:c r="C86" s="127"/>
+      <x:c r="D86" s="127"/>
+      <x:c r="E86" s="127"/>
+      <x:c r="F86" s="127"/>
+      <x:c r="G86" s="127"/>
+      <x:c r="H86" s="127"/>
+      <x:c r="I86" s="130"/>
+      <x:c r="J86" s="130"/>
+      <x:c r="K86" s="133" t="str">
+        <x:f>IF(A86="","",IF(I86="",24*(NOW()-A86),24*(I86-A86)))</x:f>
+      </x:c>
+      <x:c r="L86" s="127"/>
+      <x:c r="M86" s="127"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="130"/>
+      <x:c r="B87" s="127"/>
+      <x:c r="C87" s="127"/>
+      <x:c r="D87" s="127"/>
+      <x:c r="E87" s="127"/>
+      <x:c r="F87" s="127"/>
+      <x:c r="G87" s="127"/>
+      <x:c r="H87" s="127"/>
+      <x:c r="I87" s="130"/>
+      <x:c r="J87" s="130"/>
+      <x:c r="K87" s="133" t="str">
+        <x:f>IF(A87="","",IF(I87="",24*(NOW()-A87),24*(I87-A87)))</x:f>
+      </x:c>
+      <x:c r="L87" s="127"/>
+      <x:c r="M87" s="127"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="130"/>
+      <x:c r="B88" s="127"/>
+      <x:c r="C88" s="127"/>
+      <x:c r="D88" s="127"/>
+      <x:c r="E88" s="127"/>
+      <x:c r="F88" s="127"/>
+      <x:c r="G88" s="127"/>
+      <x:c r="H88" s="127"/>
+      <x:c r="I88" s="130"/>
+      <x:c r="J88" s="130"/>
+      <x:c r="K88" s="133" t="str">
+        <x:f>IF(A88="","",IF(I88="",24*(NOW()-A88),24*(I88-A88)))</x:f>
+      </x:c>
+      <x:c r="L88" s="127"/>
+      <x:c r="M88" s="127"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="130"/>
+      <x:c r="B89" s="127"/>
+      <x:c r="C89" s="127"/>
+      <x:c r="D89" s="127"/>
+      <x:c r="E89" s="127"/>
+      <x:c r="F89" s="127"/>
+      <x:c r="G89" s="127"/>
+      <x:c r="H89" s="127"/>
+      <x:c r="I89" s="130"/>
+      <x:c r="J89" s="130"/>
+      <x:c r="K89" s="133" t="str">
+        <x:f>IF(A89="","",IF(I89="",24*(NOW()-A89),24*(I89-A89)))</x:f>
+      </x:c>
+      <x:c r="L89" s="127"/>
+      <x:c r="M89" s="127"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="130"/>
+      <x:c r="B90" s="127"/>
+      <x:c r="C90" s="127"/>
+      <x:c r="D90" s="127"/>
+      <x:c r="E90" s="127"/>
+      <x:c r="F90" s="127"/>
+      <x:c r="G90" s="127"/>
+      <x:c r="H90" s="127"/>
+      <x:c r="I90" s="130"/>
+      <x:c r="J90" s="130"/>
+      <x:c r="K90" s="133" t="str">
+        <x:f>IF(A90="","",IF(I90="",24*(NOW()-A90),24*(I90-A90)))</x:f>
+      </x:c>
+      <x:c r="L90" s="127"/>
+      <x:c r="M90" s="127"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="130"/>
+      <x:c r="B91" s="127"/>
+      <x:c r="C91" s="127"/>
+      <x:c r="D91" s="127"/>
+      <x:c r="E91" s="127"/>
+      <x:c r="F91" s="127"/>
+      <x:c r="G91" s="127"/>
+      <x:c r="H91" s="127"/>
+      <x:c r="I91" s="130"/>
+      <x:c r="J91" s="130"/>
+      <x:c r="K91" s="133" t="str">
+        <x:f>IF(A91="","",IF(I91="",24*(NOW()-A91),24*(I91-A91)))</x:f>
+      </x:c>
+      <x:c r="L91" s="127"/>
+      <x:c r="M91" s="127"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="130"/>
+      <x:c r="B92" s="127"/>
+      <x:c r="C92" s="127"/>
+      <x:c r="D92" s="127"/>
+      <x:c r="E92" s="127"/>
+      <x:c r="F92" s="127"/>
+      <x:c r="G92" s="127"/>
+      <x:c r="H92" s="127"/>
+      <x:c r="I92" s="130"/>
+      <x:c r="J92" s="130"/>
+      <x:c r="K92" s="133" t="str">
+        <x:f>IF(A92="","",IF(I92="",24*(NOW()-A92),24*(I92-A92)))</x:f>
+      </x:c>
+      <x:c r="L92" s="127"/>
+      <x:c r="M92" s="127"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="130"/>
+      <x:c r="B93" s="127"/>
+      <x:c r="C93" s="127"/>
+      <x:c r="D93" s="127"/>
+      <x:c r="E93" s="127"/>
+      <x:c r="F93" s="127"/>
+      <x:c r="G93" s="127"/>
+      <x:c r="H93" s="127"/>
+      <x:c r="I93" s="130"/>
+      <x:c r="J93" s="130"/>
+      <x:c r="K93" s="133" t="str">
+        <x:f>IF(A93="","",IF(I93="",24*(NOW()-A93),24*(I93-A93)))</x:f>
+      </x:c>
+      <x:c r="L93" s="127"/>
+      <x:c r="M93" s="127"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="130"/>
+      <x:c r="B94" s="127"/>
+      <x:c r="C94" s="127"/>
+      <x:c r="D94" s="127"/>
+      <x:c r="E94" s="127"/>
+      <x:c r="F94" s="127"/>
+      <x:c r="G94" s="127"/>
+      <x:c r="H94" s="127"/>
+      <x:c r="I94" s="130"/>
+      <x:c r="J94" s="130"/>
+      <x:c r="K94" s="133" t="str">
+        <x:f>IF(A94="","",IF(I94="",24*(NOW()-A94),24*(I94-A94)))</x:f>
+      </x:c>
+      <x:c r="L94" s="127"/>
+      <x:c r="M94" s="127"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="130"/>
+      <x:c r="B95" s="127"/>
+      <x:c r="C95" s="127"/>
+      <x:c r="D95" s="127"/>
+      <x:c r="E95" s="127"/>
+      <x:c r="F95" s="127"/>
+      <x:c r="G95" s="127"/>
+      <x:c r="H95" s="127"/>
+      <x:c r="I95" s="130"/>
+      <x:c r="J95" s="130"/>
+      <x:c r="K95" s="133" t="str">
+        <x:f>IF(A95="","",IF(I95="",24*(NOW()-A95),24*(I95-A95)))</x:f>
+      </x:c>
+      <x:c r="L95" s="127"/>
+      <x:c r="M95" s="127"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="130"/>
+      <x:c r="B96" s="127"/>
+      <x:c r="C96" s="127"/>
+      <x:c r="D96" s="127"/>
+      <x:c r="E96" s="127"/>
+      <x:c r="F96" s="127"/>
+      <x:c r="G96" s="127"/>
+      <x:c r="H96" s="127"/>
+      <x:c r="I96" s="130"/>
+      <x:c r="J96" s="130"/>
+      <x:c r="K96" s="133" t="str">
+        <x:f>IF(A96="","",IF(I96="",24*(NOW()-A96),24*(I96-A96)))</x:f>
+      </x:c>
+      <x:c r="L96" s="127"/>
+      <x:c r="M96" s="127"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="130"/>
+      <x:c r="B97" s="127"/>
+      <x:c r="C97" s="127"/>
+      <x:c r="D97" s="127"/>
+      <x:c r="E97" s="127"/>
+      <x:c r="F97" s="127"/>
+      <x:c r="G97" s="127"/>
+      <x:c r="H97" s="127"/>
+      <x:c r="I97" s="130"/>
+      <x:c r="J97" s="130"/>
+      <x:c r="K97" s="133" t="str">
+        <x:f>IF(A97="","",IF(I97="",24*(NOW()-A97),24*(I97-A97)))</x:f>
+      </x:c>
+      <x:c r="L97" s="127"/>
+      <x:c r="M97" s="127"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="130"/>
+      <x:c r="B98" s="127"/>
+      <x:c r="C98" s="127"/>
+      <x:c r="D98" s="127"/>
+      <x:c r="E98" s="127"/>
+      <x:c r="F98" s="127"/>
+      <x:c r="G98" s="127"/>
+      <x:c r="H98" s="127"/>
+      <x:c r="I98" s="130"/>
+      <x:c r="J98" s="130"/>
+      <x:c r="K98" s="133" t="str">
+        <x:f>IF(A98="","",IF(I98="",24*(NOW()-A98),24*(I98-A98)))</x:f>
+      </x:c>
+      <x:c r="L98" s="127"/>
+      <x:c r="M98" s="127"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="130"/>
+      <x:c r="B99" s="127"/>
+      <x:c r="C99" s="127"/>
+      <x:c r="D99" s="127"/>
+      <x:c r="E99" s="127"/>
+      <x:c r="F99" s="127"/>
+      <x:c r="G99" s="127"/>
+      <x:c r="H99" s="127"/>
+      <x:c r="I99" s="130"/>
+      <x:c r="J99" s="130"/>
+      <x:c r="K99" s="133" t="str">
+        <x:f>IF(A99="","",IF(I99="",24*(NOW()-A99),24*(I99-A99)))</x:f>
+      </x:c>
+      <x:c r="L99" s="127"/>
+      <x:c r="M99" s="127"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="130"/>
+      <x:c r="B100" s="127"/>
+      <x:c r="C100" s="127"/>
+      <x:c r="D100" s="127"/>
+      <x:c r="E100" s="127"/>
+      <x:c r="F100" s="127"/>
+      <x:c r="G100" s="127"/>
+      <x:c r="H100" s="127"/>
+      <x:c r="I100" s="130"/>
+      <x:c r="J100" s="130"/>
+      <x:c r="K100" s="133" t="str">
+        <x:f>IF(A100="","",IF(I100="",24*(NOW()-A100),24*(I100-A100)))</x:f>
+      </x:c>
+      <x:c r="L100" s="127"/>
+      <x:c r="M100" s="127"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="130"/>
+      <x:c r="B101" s="127"/>
+      <x:c r="C101" s="127"/>
+      <x:c r="D101" s="127"/>
+      <x:c r="E101" s="127"/>
+      <x:c r="F101" s="127"/>
+      <x:c r="G101" s="127"/>
+      <x:c r="H101" s="127"/>
+      <x:c r="I101" s="130"/>
+      <x:c r="J101" s="130"/>
+      <x:c r="K101" s="133" t="str">
+        <x:f>IF(A101="","",IF(I101="",24*(NOW()-A101),24*(I101-A101)))</x:f>
+      </x:c>
+      <x:c r="L101" s="127"/>
+      <x:c r="M101" s="127"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="130"/>
+      <x:c r="B102" s="127"/>
+      <x:c r="C102" s="127"/>
+      <x:c r="D102" s="127"/>
+      <x:c r="E102" s="127"/>
+      <x:c r="F102" s="127"/>
+      <x:c r="G102" s="127"/>
+      <x:c r="H102" s="127"/>
+      <x:c r="I102" s="130"/>
+      <x:c r="J102" s="130"/>
+      <x:c r="K102" s="133" t="str">
+        <x:f>IF(A102="","",IF(I102="",24*(NOW()-A102),24*(I102-A102)))</x:f>
+      </x:c>
+      <x:c r="L102" s="127"/>
+      <x:c r="M102" s="127"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="130"/>
+      <x:c r="B103" s="127"/>
+      <x:c r="C103" s="127"/>
+      <x:c r="D103" s="127"/>
+      <x:c r="E103" s="127"/>
+      <x:c r="F103" s="127"/>
+      <x:c r="G103" s="127"/>
+      <x:c r="H103" s="127"/>
+      <x:c r="I103" s="130"/>
+      <x:c r="J103" s="130"/>
+      <x:c r="K103" s="133" t="str">
+        <x:f>IF(A103="","",IF(I103="",24*(NOW()-A103),24*(I103-A103)))</x:f>
+      </x:c>
+      <x:c r="L103" s="127"/>
+      <x:c r="M103" s="127"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="131"/>
+      <x:c r="B104" s="128"/>
+      <x:c r="C104" s="128"/>
+      <x:c r="D104" s="128"/>
+      <x:c r="E104" s="128"/>
+      <x:c r="F104" s="128"/>
+      <x:c r="G104" s="128"/>
+      <x:c r="H104" s="128"/>
+      <x:c r="I104" s="131"/>
+      <x:c r="J104" s="131"/>
+      <x:c r="K104" s="134" t="str">
+        <x:f>IF(A104="","",IF(I104="",24*(NOW()-A104),24*(I104-A104)))</x:f>
+      </x:c>
+      <x:c r="L104" s="128"/>
+      <x:c r="M104" s="128"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:M1"/>
+    <x:mergeCell ref="A2:M2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="F5:F104">
+    <x:cfRule type="containsText" dxfId="96" priority="1" operator="containsText" text="P0"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G5:G104">
+    <x:cfRule type="containsText" dxfId="97" priority="2" operator="containsText" text="Закрыто"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="5">
+    <x:dataValidation type="list" sqref="D5:D104">
+      <x:formula1>"@weezSup,Weez Poker Chat,Личное сообщение,Другое"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E5:E104">
+      <x:formula1>"Техника,Деньги,Игра,Аккаунт,Другое"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F5:F104">
+      <x:formula1>"P0,P1,P2,P3"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G5:G104">
+      <x:formula1>"Новое,В работе,Ожидает игрока,Решено,Закрыто"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H5:H104">
+      <x:formula1>"Владелец,Помощник"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca87c15e1424469a"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="26" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="26" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="113" t="str">
+        <x:v>Incident Register</x:v>
+      </x:c>
+      <x:c r="B1" s="113"/>
+      <x:c r="C1" s="113"/>
+      <x:c r="D1" s="113"/>
+      <x:c r="E1" s="113"/>
+      <x:c r="F1" s="113"/>
+      <x:c r="G1" s="113"/>
+      <x:c r="H1" s="113"/>
+      <x:c r="I1" s="113"/>
+      <x:c r="J1" s="113"/>
+      <x:c r="K1" s="113"/>
+      <x:c r="L1" s="113"/>
+      <x:c r="M1" s="113"/>
+      <x:c r="N1" s="113"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="116" t="str">
+        <x:v>P0 останавливает Cash. Каждый инцидент получает владельца, хронологию, исправление и проверку.</x:v>
+      </x:c>
+      <x:c r="B2" s="116"/>
+      <x:c r="C2" s="116"/>
+      <x:c r="D2" s="116"/>
+      <x:c r="E2" s="116"/>
+      <x:c r="F2" s="116"/>
+      <x:c r="G2" s="116"/>
+      <x:c r="H2" s="116"/>
+      <x:c r="I2" s="116"/>
+      <x:c r="J2" s="116"/>
+      <x:c r="K2" s="116"/>
+      <x:c r="L2" s="116"/>
+      <x:c r="M2" s="116"/>
+      <x:c r="N2" s="116"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="120" t="str">
+        <x:v>Opened at</x:v>
+      </x:c>
+      <x:c r="B4" s="120" t="str">
+        <x:v>Incident ID</x:v>
+      </x:c>
+      <x:c r="C4" s="120" t="str">
+        <x:v>Severity</x:v>
+      </x:c>
+      <x:c r="D4" s="120" t="str">
+        <x:v>Surface</x:v>
+      </x:c>
+      <x:c r="E4" s="120" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="F4" s="120" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="G4" s="120" t="str">
+        <x:v>Users affected</x:v>
+      </x:c>
+      <x:c r="H4" s="120" t="str">
+        <x:v>Money affected $</x:v>
+      </x:c>
+      <x:c r="I4" s="120" t="str">
+        <x:v>Detection</x:v>
+      </x:c>
+      <x:c r="J4" s="120" t="str">
+        <x:v>Root cause</x:v>
+      </x:c>
+      <x:c r="K4" s="120" t="str">
+        <x:v>Mitigation</x:v>
+      </x:c>
+      <x:c r="L4" s="120" t="str">
+        <x:v>Resolved at</x:v>
+      </x:c>
+      <x:c r="M4" s="120" t="str">
+        <x:v>Postmortem</x:v>
+      </x:c>
+      <x:c r="N4" s="120" t="str">
+        <x:v>Evidence link</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="129"/>
+      <x:c r="B5" s="126"/>
+      <x:c r="C5" s="126"/>
+      <x:c r="D5" s="126"/>
+      <x:c r="E5" s="126"/>
+      <x:c r="F5" s="126"/>
+      <x:c r="G5" s="126"/>
+      <x:c r="H5" s="135"/>
+      <x:c r="I5" s="126"/>
+      <x:c r="J5" s="126"/>
+      <x:c r="K5" s="126"/>
+      <x:c r="L5" s="129"/>
+      <x:c r="M5" s="126"/>
+      <x:c r="N5" s="126"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="130"/>
+      <x:c r="B6" s="127"/>
+      <x:c r="C6" s="127"/>
+      <x:c r="D6" s="127"/>
+      <x:c r="E6" s="127"/>
+      <x:c r="F6" s="127"/>
+      <x:c r="G6" s="127"/>
+      <x:c r="H6" s="136"/>
+      <x:c r="I6" s="127"/>
+      <x:c r="J6" s="127"/>
+      <x:c r="K6" s="127"/>
+      <x:c r="L6" s="130"/>
+      <x:c r="M6" s="127"/>
+      <x:c r="N6" s="127"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="130"/>
+      <x:c r="B7" s="127"/>
+      <x:c r="C7" s="127"/>
+      <x:c r="D7" s="127"/>
+      <x:c r="E7" s="127"/>
+      <x:c r="F7" s="127"/>
+      <x:c r="G7" s="127"/>
+      <x:c r="H7" s="136"/>
+      <x:c r="I7" s="127"/>
+      <x:c r="J7" s="127"/>
+      <x:c r="K7" s="127"/>
+      <x:c r="L7" s="130"/>
+      <x:c r="M7" s="127"/>
+      <x:c r="N7" s="127"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="130"/>
+      <x:c r="B8" s="127"/>
+      <x:c r="C8" s="127"/>
+      <x:c r="D8" s="127"/>
+      <x:c r="E8" s="127"/>
+      <x:c r="F8" s="127"/>
+      <x:c r="G8" s="127"/>
+      <x:c r="H8" s="136"/>
+      <x:c r="I8" s="127"/>
+      <x:c r="J8" s="127"/>
+      <x:c r="K8" s="127"/>
+      <x:c r="L8" s="130"/>
+      <x:c r="M8" s="127"/>
+      <x:c r="N8" s="127"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="130"/>
+      <x:c r="B9" s="127"/>
+      <x:c r="C9" s="127"/>
+      <x:c r="D9" s="127"/>
+      <x:c r="E9" s="127"/>
+      <x:c r="F9" s="127"/>
+      <x:c r="G9" s="127"/>
+      <x:c r="H9" s="136"/>
+      <x:c r="I9" s="127"/>
+      <x:c r="J9" s="127"/>
+      <x:c r="K9" s="127"/>
+      <x:c r="L9" s="130"/>
+      <x:c r="M9" s="127"/>
+      <x:c r="N9" s="127"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="130"/>
+      <x:c r="B10" s="127"/>
+      <x:c r="C10" s="127"/>
+      <x:c r="D10" s="127"/>
+      <x:c r="E10" s="127"/>
+      <x:c r="F10" s="127"/>
+      <x:c r="G10" s="127"/>
+      <x:c r="H10" s="136"/>
+      <x:c r="I10" s="127"/>
+      <x:c r="J10" s="127"/>
+      <x:c r="K10" s="127"/>
+      <x:c r="L10" s="130"/>
+      <x:c r="M10" s="127"/>
+      <x:c r="N10" s="127"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="130"/>
+      <x:c r="B11" s="127"/>
+      <x:c r="C11" s="127"/>
+      <x:c r="D11" s="127"/>
+      <x:c r="E11" s="127"/>
+      <x:c r="F11" s="127"/>
+      <x:c r="G11" s="127"/>
+      <x:c r="H11" s="136"/>
+      <x:c r="I11" s="127"/>
+      <x:c r="J11" s="127"/>
+      <x:c r="K11" s="127"/>
+      <x:c r="L11" s="130"/>
+      <x:c r="M11" s="127"/>
+      <x:c r="N11" s="127"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="130"/>
+      <x:c r="B12" s="127"/>
+      <x:c r="C12" s="127"/>
+      <x:c r="D12" s="127"/>
+      <x:c r="E12" s="127"/>
+      <x:c r="F12" s="127"/>
+      <x:c r="G12" s="127"/>
+      <x:c r="H12" s="136"/>
+      <x:c r="I12" s="127"/>
+      <x:c r="J12" s="127"/>
+      <x:c r="K12" s="127"/>
+      <x:c r="L12" s="130"/>
+      <x:c r="M12" s="127"/>
+      <x:c r="N12" s="127"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="130"/>
+      <x:c r="B13" s="127"/>
+      <x:c r="C13" s="127"/>
+      <x:c r="D13" s="127"/>
+      <x:c r="E13" s="127"/>
+      <x:c r="F13" s="127"/>
+      <x:c r="G13" s="127"/>
+      <x:c r="H13" s="136"/>
+      <x:c r="I13" s="127"/>
+      <x:c r="J13" s="127"/>
+      <x:c r="K13" s="127"/>
+      <x:c r="L13" s="130"/>
+      <x:c r="M13" s="127"/>
+      <x:c r="N13" s="127"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="130"/>
+      <x:c r="B14" s="127"/>
+      <x:c r="C14" s="127"/>
+      <x:c r="D14" s="127"/>
+      <x:c r="E14" s="127"/>
+      <x:c r="F14" s="127"/>
+      <x:c r="G14" s="127"/>
+      <x:c r="H14" s="136"/>
+      <x:c r="I14" s="127"/>
+      <x:c r="J14" s="127"/>
+      <x:c r="K14" s="127"/>
+      <x:c r="L14" s="130"/>
+      <x:c r="M14" s="127"/>
+      <x:c r="N14" s="127"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="130"/>
+      <x:c r="B15" s="127"/>
+      <x:c r="C15" s="127"/>
+      <x:c r="D15" s="127"/>
+      <x:c r="E15" s="127"/>
+      <x:c r="F15" s="127"/>
+      <x:c r="G15" s="127"/>
+      <x:c r="H15" s="136"/>
+      <x:c r="I15" s="127"/>
+      <x:c r="J15" s="127"/>
+      <x:c r="K15" s="127"/>
+      <x:c r="L15" s="130"/>
+      <x:c r="M15" s="127"/>
+      <x:c r="N15" s="127"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="130"/>
+      <x:c r="B16" s="127"/>
+      <x:c r="C16" s="127"/>
+      <x:c r="D16" s="127"/>
+      <x:c r="E16" s="127"/>
+      <x:c r="F16" s="127"/>
+      <x:c r="G16" s="127"/>
+      <x:c r="H16" s="136"/>
+      <x:c r="I16" s="127"/>
+      <x:c r="J16" s="127"/>
+      <x:c r="K16" s="127"/>
+      <x:c r="L16" s="130"/>
+      <x:c r="M16" s="127"/>
+      <x:c r="N16" s="127"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="130"/>
+      <x:c r="B17" s="127"/>
+      <x:c r="C17" s="127"/>
+      <x:c r="D17" s="127"/>
+      <x:c r="E17" s="127"/>
+      <x:c r="F17" s="127"/>
+      <x:c r="G17" s="127"/>
+      <x:c r="H17" s="136"/>
+      <x:c r="I17" s="127"/>
+      <x:c r="J17" s="127"/>
+      <x:c r="K17" s="127"/>
+      <x:c r="L17" s="130"/>
+      <x:c r="M17" s="127"/>
+      <x:c r="N17" s="127"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="130"/>
+      <x:c r="B18" s="127"/>
+      <x:c r="C18" s="127"/>
+      <x:c r="D18" s="127"/>
+      <x:c r="E18" s="127"/>
+      <x:c r="F18" s="127"/>
+      <x:c r="G18" s="127"/>
+      <x:c r="H18" s="136"/>
+      <x:c r="I18" s="127"/>
+      <x:c r="J18" s="127"/>
+      <x:c r="K18" s="127"/>
+      <x:c r="L18" s="130"/>
+      <x:c r="M18" s="127"/>
+      <x:c r="N18" s="127"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="130"/>
+      <x:c r="B19" s="127"/>
+      <x:c r="C19" s="127"/>
+      <x:c r="D19" s="127"/>
+      <x:c r="E19" s="127"/>
+      <x:c r="F19" s="127"/>
+      <x:c r="G19" s="127"/>
+      <x:c r="H19" s="136"/>
+      <x:c r="I19" s="127"/>
+      <x:c r="J19" s="127"/>
+      <x:c r="K19" s="127"/>
+      <x:c r="L19" s="130"/>
+      <x:c r="M19" s="127"/>
+      <x:c r="N19" s="127"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="130"/>
+      <x:c r="B20" s="127"/>
+      <x:c r="C20" s="127"/>
+      <x:c r="D20" s="127"/>
+      <x:c r="E20" s="127"/>
+      <x:c r="F20" s="127"/>
+      <x:c r="G20" s="127"/>
+      <x:c r="H20" s="136"/>
+      <x:c r="I20" s="127"/>
+      <x:c r="J20" s="127"/>
+      <x:c r="K20" s="127"/>
+      <x:c r="L20" s="130"/>
+      <x:c r="M20" s="127"/>
+      <x:c r="N20" s="127"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="130"/>
+      <x:c r="B21" s="127"/>
+      <x:c r="C21" s="127"/>
+      <x:c r="D21" s="127"/>
+      <x:c r="E21" s="127"/>
+      <x:c r="F21" s="127"/>
+      <x:c r="G21" s="127"/>
+      <x:c r="H21" s="136"/>
+      <x:c r="I21" s="127"/>
+      <x:c r="J21" s="127"/>
+      <x:c r="K21" s="127"/>
+      <x:c r="L21" s="130"/>
+      <x:c r="M21" s="127"/>
+      <x:c r="N21" s="127"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="130"/>
+      <x:c r="B22" s="127"/>
+      <x:c r="C22" s="127"/>
+      <x:c r="D22" s="127"/>
+      <x:c r="E22" s="127"/>
+      <x:c r="F22" s="127"/>
+      <x:c r="G22" s="127"/>
+      <x:c r="H22" s="136"/>
+      <x:c r="I22" s="127"/>
+      <x:c r="J22" s="127"/>
+      <x:c r="K22" s="127"/>
+      <x:c r="L22" s="130"/>
+      <x:c r="M22" s="127"/>
+      <x:c r="N22" s="127"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="130"/>
+      <x:c r="B23" s="127"/>
+      <x:c r="C23" s="127"/>
+      <x:c r="D23" s="127"/>
+      <x:c r="E23" s="127"/>
+      <x:c r="F23" s="127"/>
+      <x:c r="G23" s="127"/>
+      <x:c r="H23" s="136"/>
+      <x:c r="I23" s="127"/>
+      <x:c r="J23" s="127"/>
+      <x:c r="K23" s="127"/>
+      <x:c r="L23" s="130"/>
+      <x:c r="M23" s="127"/>
+      <x:c r="N23" s="127"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="130"/>
+      <x:c r="B24" s="127"/>
+      <x:c r="C24" s="127"/>
+      <x:c r="D24" s="127"/>
+      <x:c r="E24" s="127"/>
+      <x:c r="F24" s="127"/>
+      <x:c r="G24" s="127"/>
+      <x:c r="H24" s="136"/>
+      <x:c r="I24" s="127"/>
+      <x:c r="J24" s="127"/>
+      <x:c r="K24" s="127"/>
+      <x:c r="L24" s="130"/>
+      <x:c r="M24" s="127"/>
+      <x:c r="N24" s="127"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="130"/>
+      <x:c r="B25" s="127"/>
+      <x:c r="C25" s="127"/>
+      <x:c r="D25" s="127"/>
+      <x:c r="E25" s="127"/>
+      <x:c r="F25" s="127"/>
+      <x:c r="G25" s="127"/>
+      <x:c r="H25" s="136"/>
+      <x:c r="I25" s="127"/>
+      <x:c r="J25" s="127"/>
+      <x:c r="K25" s="127"/>
+      <x:c r="L25" s="130"/>
+      <x:c r="M25" s="127"/>
+      <x:c r="N25" s="127"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="130"/>
+      <x:c r="B26" s="127"/>
+      <x:c r="C26" s="127"/>
+      <x:c r="D26" s="127"/>
+      <x:c r="E26" s="127"/>
+      <x:c r="F26" s="127"/>
+      <x:c r="G26" s="127"/>
+      <x:c r="H26" s="136"/>
+      <x:c r="I26" s="127"/>
+      <x:c r="J26" s="127"/>
+      <x:c r="K26" s="127"/>
+      <x:c r="L26" s="130"/>
+      <x:c r="M26" s="127"/>
+      <x:c r="N26" s="127"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="130"/>
+      <x:c r="B27" s="127"/>
+      <x:c r="C27" s="127"/>
+      <x:c r="D27" s="127"/>
+      <x:c r="E27" s="127"/>
+      <x:c r="F27" s="127"/>
+      <x:c r="G27" s="127"/>
+      <x:c r="H27" s="136"/>
+      <x:c r="I27" s="127"/>
+      <x:c r="J27" s="127"/>
+      <x:c r="K27" s="127"/>
+      <x:c r="L27" s="130"/>
+      <x:c r="M27" s="127"/>
+      <x:c r="N27" s="127"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="130"/>
+      <x:c r="B28" s="127"/>
+      <x:c r="C28" s="127"/>
+      <x:c r="D28" s="127"/>
+      <x:c r="E28" s="127"/>
+      <x:c r="F28" s="127"/>
+      <x:c r="G28" s="127"/>
+      <x:c r="H28" s="136"/>
+      <x:c r="I28" s="127"/>
+      <x:c r="J28" s="127"/>
+      <x:c r="K28" s="127"/>
+      <x:c r="L28" s="130"/>
+      <x:c r="M28" s="127"/>
+      <x:c r="N28" s="127"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="130"/>
+      <x:c r="B29" s="127"/>
+      <x:c r="C29" s="127"/>
+      <x:c r="D29" s="127"/>
+      <x:c r="E29" s="127"/>
+      <x:c r="F29" s="127"/>
+      <x:c r="G29" s="127"/>
+      <x:c r="H29" s="136"/>
+      <x:c r="I29" s="127"/>
+      <x:c r="J29" s="127"/>
+      <x:c r="K29" s="127"/>
+      <x:c r="L29" s="130"/>
+      <x:c r="M29" s="127"/>
+      <x:c r="N29" s="127"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="130"/>
+      <x:c r="B30" s="127"/>
+      <x:c r="C30" s="127"/>
+      <x:c r="D30" s="127"/>
+      <x:c r="E30" s="127"/>
+      <x:c r="F30" s="127"/>
+      <x:c r="G30" s="127"/>
+      <x:c r="H30" s="136"/>
+      <x:c r="I30" s="127"/>
+      <x:c r="J30" s="127"/>
+      <x:c r="K30" s="127"/>
+      <x:c r="L30" s="130"/>
+      <x:c r="M30" s="127"/>
+      <x:c r="N30" s="127"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="130"/>
+      <x:c r="B31" s="127"/>
+      <x:c r="C31" s="127"/>
+      <x:c r="D31" s="127"/>
+      <x:c r="E31" s="127"/>
+      <x:c r="F31" s="127"/>
+      <x:c r="G31" s="127"/>
+      <x:c r="H31" s="136"/>
+      <x:c r="I31" s="127"/>
+      <x:c r="J31" s="127"/>
+      <x:c r="K31" s="127"/>
+      <x:c r="L31" s="130"/>
+      <x:c r="M31" s="127"/>
+      <x:c r="N31" s="127"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="130"/>
+      <x:c r="B32" s="127"/>
+      <x:c r="C32" s="127"/>
+      <x:c r="D32" s="127"/>
+      <x:c r="E32" s="127"/>
+      <x:c r="F32" s="127"/>
+      <x:c r="G32" s="127"/>
+      <x:c r="H32" s="136"/>
+      <x:c r="I32" s="127"/>
+      <x:c r="J32" s="127"/>
+      <x:c r="K32" s="127"/>
+      <x:c r="L32" s="130"/>
+      <x:c r="M32" s="127"/>
+      <x:c r="N32" s="127"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="130"/>
+      <x:c r="B33" s="127"/>
+      <x:c r="C33" s="127"/>
+      <x:c r="D33" s="127"/>
+      <x:c r="E33" s="127"/>
+      <x:c r="F33" s="127"/>
+      <x:c r="G33" s="127"/>
+      <x:c r="H33" s="136"/>
+      <x:c r="I33" s="127"/>
+      <x:c r="J33" s="127"/>
+      <x:c r="K33" s="127"/>
+      <x:c r="L33" s="130"/>
+      <x:c r="M33" s="127"/>
+      <x:c r="N33" s="127"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="130"/>
+      <x:c r="B34" s="127"/>
+      <x:c r="C34" s="127"/>
+      <x:c r="D34" s="127"/>
+      <x:c r="E34" s="127"/>
+      <x:c r="F34" s="127"/>
+      <x:c r="G34" s="127"/>
+      <x:c r="H34" s="136"/>
+      <x:c r="I34" s="127"/>
+      <x:c r="J34" s="127"/>
+      <x:c r="K34" s="127"/>
+      <x:c r="L34" s="130"/>
+      <x:c r="M34" s="127"/>
+      <x:c r="N34" s="127"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="130"/>
+      <x:c r="B35" s="127"/>
+      <x:c r="C35" s="127"/>
+      <x:c r="D35" s="127"/>
+      <x:c r="E35" s="127"/>
+      <x:c r="F35" s="127"/>
+      <x:c r="G35" s="127"/>
+      <x:c r="H35" s="136"/>
+      <x:c r="I35" s="127"/>
+      <x:c r="J35" s="127"/>
+      <x:c r="K35" s="127"/>
+      <x:c r="L35" s="130"/>
+      <x:c r="M35" s="127"/>
+      <x:c r="N35" s="127"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="130"/>
+      <x:c r="B36" s="127"/>
+      <x:c r="C36" s="127"/>
+      <x:c r="D36" s="127"/>
+      <x:c r="E36" s="127"/>
+      <x:c r="F36" s="127"/>
+      <x:c r="G36" s="127"/>
+      <x:c r="H36" s="136"/>
+      <x:c r="I36" s="127"/>
+      <x:c r="J36" s="127"/>
+      <x:c r="K36" s="127"/>
+      <x:c r="L36" s="130"/>
+      <x:c r="M36" s="127"/>
+      <x:c r="N36" s="127"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="130"/>
+      <x:c r="B37" s="127"/>
+      <x:c r="C37" s="127"/>
+      <x:c r="D37" s="127"/>
+      <x:c r="E37" s="127"/>
+      <x:c r="F37" s="127"/>
+      <x:c r="G37" s="127"/>
+      <x:c r="H37" s="136"/>
+      <x:c r="I37" s="127"/>
+      <x:c r="J37" s="127"/>
+      <x:c r="K37" s="127"/>
+      <x:c r="L37" s="130"/>
+      <x:c r="M37" s="127"/>
+      <x:c r="N37" s="127"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="130"/>
+      <x:c r="B38" s="127"/>
+      <x:c r="C38" s="127"/>
+      <x:c r="D38" s="127"/>
+      <x:c r="E38" s="127"/>
+      <x:c r="F38" s="127"/>
+      <x:c r="G38" s="127"/>
+      <x:c r="H38" s="136"/>
+      <x:c r="I38" s="127"/>
+      <x:c r="J38" s="127"/>
+      <x:c r="K38" s="127"/>
+      <x:c r="L38" s="130"/>
+      <x:c r="M38" s="127"/>
+      <x:c r="N38" s="127"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="130"/>
+      <x:c r="B39" s="127"/>
+      <x:c r="C39" s="127"/>
+      <x:c r="D39" s="127"/>
+      <x:c r="E39" s="127"/>
+      <x:c r="F39" s="127"/>
+      <x:c r="G39" s="127"/>
+      <x:c r="H39" s="136"/>
+      <x:c r="I39" s="127"/>
+      <x:c r="J39" s="127"/>
+      <x:c r="K39" s="127"/>
+      <x:c r="L39" s="130"/>
+      <x:c r="M39" s="127"/>
+      <x:c r="N39" s="127"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="130"/>
+      <x:c r="B40" s="127"/>
+      <x:c r="C40" s="127"/>
+      <x:c r="D40" s="127"/>
+      <x:c r="E40" s="127"/>
+      <x:c r="F40" s="127"/>
+      <x:c r="G40" s="127"/>
+      <x:c r="H40" s="136"/>
+      <x:c r="I40" s="127"/>
+      <x:c r="J40" s="127"/>
+      <x:c r="K40" s="127"/>
+      <x:c r="L40" s="130"/>
+      <x:c r="M40" s="127"/>
+      <x:c r="N40" s="127"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="130"/>
+      <x:c r="B41" s="127"/>
+      <x:c r="C41" s="127"/>
+      <x:c r="D41" s="127"/>
+      <x:c r="E41" s="127"/>
+      <x:c r="F41" s="127"/>
+      <x:c r="G41" s="127"/>
+      <x:c r="H41" s="136"/>
+      <x:c r="I41" s="127"/>
+      <x:c r="J41" s="127"/>
+      <x:c r="K41" s="127"/>
+      <x:c r="L41" s="130"/>
+      <x:c r="M41" s="127"/>
+      <x:c r="N41" s="127"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="130"/>
+      <x:c r="B42" s="127"/>
+      <x:c r="C42" s="127"/>
+      <x:c r="D42" s="127"/>
+      <x:c r="E42" s="127"/>
+      <x:c r="F42" s="127"/>
+      <x:c r="G42" s="127"/>
+      <x:c r="H42" s="136"/>
+      <x:c r="I42" s="127"/>
+      <x:c r="J42" s="127"/>
+      <x:c r="K42" s="127"/>
+      <x:c r="L42" s="130"/>
+      <x:c r="M42" s="127"/>
+      <x:c r="N42" s="127"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="130"/>
+      <x:c r="B43" s="127"/>
+      <x:c r="C43" s="127"/>
+      <x:c r="D43" s="127"/>
+      <x:c r="E43" s="127"/>
+      <x:c r="F43" s="127"/>
+      <x:c r="G43" s="127"/>
+      <x:c r="H43" s="136"/>
+      <x:c r="I43" s="127"/>
+      <x:c r="J43" s="127"/>
+      <x:c r="K43" s="127"/>
+      <x:c r="L43" s="130"/>
+      <x:c r="M43" s="127"/>
+      <x:c r="N43" s="127"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="130"/>
+      <x:c r="B44" s="127"/>
+      <x:c r="C44" s="127"/>
+      <x:c r="D44" s="127"/>
+      <x:c r="E44" s="127"/>
+      <x:c r="F44" s="127"/>
+      <x:c r="G44" s="127"/>
+      <x:c r="H44" s="136"/>
+      <x:c r="I44" s="127"/>
+      <x:c r="J44" s="127"/>
+      <x:c r="K44" s="127"/>
+      <x:c r="L44" s="130"/>
+      <x:c r="M44" s="127"/>
+      <x:c r="N44" s="127"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="130"/>
+      <x:c r="B45" s="127"/>
+      <x:c r="C45" s="127"/>
+      <x:c r="D45" s="127"/>
+      <x:c r="E45" s="127"/>
+      <x:c r="F45" s="127"/>
+      <x:c r="G45" s="127"/>
+      <x:c r="H45" s="136"/>
+      <x:c r="I45" s="127"/>
+      <x:c r="J45" s="127"/>
+      <x:c r="K45" s="127"/>
+      <x:c r="L45" s="130"/>
+      <x:c r="M45" s="127"/>
+      <x:c r="N45" s="127"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="130"/>
+      <x:c r="B46" s="127"/>
+      <x:c r="C46" s="127"/>
+      <x:c r="D46" s="127"/>
+      <x:c r="E46" s="127"/>
+      <x:c r="F46" s="127"/>
+      <x:c r="G46" s="127"/>
+      <x:c r="H46" s="136"/>
+      <x:c r="I46" s="127"/>
+      <x:c r="J46" s="127"/>
+      <x:c r="K46" s="127"/>
+      <x:c r="L46" s="130"/>
+      <x:c r="M46" s="127"/>
+      <x:c r="N46" s="127"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="130"/>
+      <x:c r="B47" s="127"/>
+      <x:c r="C47" s="127"/>
+      <x:c r="D47" s="127"/>
+      <x:c r="E47" s="127"/>
+      <x:c r="F47" s="127"/>
+      <x:c r="G47" s="127"/>
+      <x:c r="H47" s="136"/>
+      <x:c r="I47" s="127"/>
+      <x:c r="J47" s="127"/>
+      <x:c r="K47" s="127"/>
+      <x:c r="L47" s="130"/>
+      <x:c r="M47" s="127"/>
+      <x:c r="N47" s="127"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="130"/>
+      <x:c r="B48" s="127"/>
+      <x:c r="C48" s="127"/>
+      <x:c r="D48" s="127"/>
+      <x:c r="E48" s="127"/>
+      <x:c r="F48" s="127"/>
+      <x:c r="G48" s="127"/>
+      <x:c r="H48" s="136"/>
+      <x:c r="I48" s="127"/>
+      <x:c r="J48" s="127"/>
+      <x:c r="K48" s="127"/>
+      <x:c r="L48" s="130"/>
+      <x:c r="M48" s="127"/>
+      <x:c r="N48" s="127"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="130"/>
+      <x:c r="B49" s="127"/>
+      <x:c r="C49" s="127"/>
+      <x:c r="D49" s="127"/>
+      <x:c r="E49" s="127"/>
+      <x:c r="F49" s="127"/>
+      <x:c r="G49" s="127"/>
+      <x:c r="H49" s="136"/>
+      <x:c r="I49" s="127"/>
+      <x:c r="J49" s="127"/>
+      <x:c r="K49" s="127"/>
+      <x:c r="L49" s="130"/>
+      <x:c r="M49" s="127"/>
+      <x:c r="N49" s="127"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="130"/>
+      <x:c r="B50" s="127"/>
+      <x:c r="C50" s="127"/>
+      <x:c r="D50" s="127"/>
+      <x:c r="E50" s="127"/>
+      <x:c r="F50" s="127"/>
+      <x:c r="G50" s="127"/>
+      <x:c r="H50" s="136"/>
+      <x:c r="I50" s="127"/>
+      <x:c r="J50" s="127"/>
+      <x:c r="K50" s="127"/>
+      <x:c r="L50" s="130"/>
+      <x:c r="M50" s="127"/>
+      <x:c r="N50" s="127"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="130"/>
+      <x:c r="B51" s="127"/>
+      <x:c r="C51" s="127"/>
+      <x:c r="D51" s="127"/>
+      <x:c r="E51" s="127"/>
+      <x:c r="F51" s="127"/>
+      <x:c r="G51" s="127"/>
+      <x:c r="H51" s="136"/>
+      <x:c r="I51" s="127"/>
+      <x:c r="J51" s="127"/>
+      <x:c r="K51" s="127"/>
+      <x:c r="L51" s="130"/>
+      <x:c r="M51" s="127"/>
+      <x:c r="N51" s="127"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="130"/>
+      <x:c r="B52" s="127"/>
+      <x:c r="C52" s="127"/>
+      <x:c r="D52" s="127"/>
+      <x:c r="E52" s="127"/>
+      <x:c r="F52" s="127"/>
+      <x:c r="G52" s="127"/>
+      <x:c r="H52" s="136"/>
+      <x:c r="I52" s="127"/>
+      <x:c r="J52" s="127"/>
+      <x:c r="K52" s="127"/>
+      <x:c r="L52" s="130"/>
+      <x:c r="M52" s="127"/>
+      <x:c r="N52" s="127"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="130"/>
+      <x:c r="B53" s="127"/>
+      <x:c r="C53" s="127"/>
+      <x:c r="D53" s="127"/>
+      <x:c r="E53" s="127"/>
+      <x:c r="F53" s="127"/>
+      <x:c r="G53" s="127"/>
+      <x:c r="H53" s="136"/>
+      <x:c r="I53" s="127"/>
+      <x:c r="J53" s="127"/>
+      <x:c r="K53" s="127"/>
+      <x:c r="L53" s="130"/>
+      <x:c r="M53" s="127"/>
+      <x:c r="N53" s="127"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="130"/>
+      <x:c r="B54" s="127"/>
+      <x:c r="C54" s="127"/>
+      <x:c r="D54" s="127"/>
+      <x:c r="E54" s="127"/>
+      <x:c r="F54" s="127"/>
+      <x:c r="G54" s="127"/>
+      <x:c r="H54" s="136"/>
+      <x:c r="I54" s="127"/>
+      <x:c r="J54" s="127"/>
+      <x:c r="K54" s="127"/>
+      <x:c r="L54" s="130"/>
+      <x:c r="M54" s="127"/>
+      <x:c r="N54" s="127"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="130"/>
+      <x:c r="B55" s="127"/>
+      <x:c r="C55" s="127"/>
+      <x:c r="D55" s="127"/>
+      <x:c r="E55" s="127"/>
+      <x:c r="F55" s="127"/>
+      <x:c r="G55" s="127"/>
+      <x:c r="H55" s="136"/>
+      <x:c r="I55" s="127"/>
+      <x:c r="J55" s="127"/>
+      <x:c r="K55" s="127"/>
+      <x:c r="L55" s="130"/>
+      <x:c r="M55" s="127"/>
+      <x:c r="N55" s="127"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="130"/>
+      <x:c r="B56" s="127"/>
+      <x:c r="C56" s="127"/>
+      <x:c r="D56" s="127"/>
+      <x:c r="E56" s="127"/>
+      <x:c r="F56" s="127"/>
+      <x:c r="G56" s="127"/>
+      <x:c r="H56" s="136"/>
+      <x:c r="I56" s="127"/>
+      <x:c r="J56" s="127"/>
+      <x:c r="K56" s="127"/>
+      <x:c r="L56" s="130"/>
+      <x:c r="M56" s="127"/>
+      <x:c r="N56" s="127"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="130"/>
+      <x:c r="B57" s="127"/>
+      <x:c r="C57" s="127"/>
+      <x:c r="D57" s="127"/>
+      <x:c r="E57" s="127"/>
+      <x:c r="F57" s="127"/>
+      <x:c r="G57" s="127"/>
+      <x:c r="H57" s="136"/>
+      <x:c r="I57" s="127"/>
+      <x:c r="J57" s="127"/>
+      <x:c r="K57" s="127"/>
+      <x:c r="L57" s="130"/>
+      <x:c r="M57" s="127"/>
+      <x:c r="N57" s="127"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="130"/>
+      <x:c r="B58" s="127"/>
+      <x:c r="C58" s="127"/>
+      <x:c r="D58" s="127"/>
+      <x:c r="E58" s="127"/>
+      <x:c r="F58" s="127"/>
+      <x:c r="G58" s="127"/>
+      <x:c r="H58" s="136"/>
+      <x:c r="I58" s="127"/>
+      <x:c r="J58" s="127"/>
+      <x:c r="K58" s="127"/>
+      <x:c r="L58" s="130"/>
+      <x:c r="M58" s="127"/>
+      <x:c r="N58" s="127"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="130"/>
+      <x:c r="B59" s="127"/>
+      <x:c r="C59" s="127"/>
+      <x:c r="D59" s="127"/>
+      <x:c r="E59" s="127"/>
+      <x:c r="F59" s="127"/>
+      <x:c r="G59" s="127"/>
+      <x:c r="H59" s="136"/>
+      <x:c r="I59" s="127"/>
+      <x:c r="J59" s="127"/>
+      <x:c r="K59" s="127"/>
+      <x:c r="L59" s="130"/>
+      <x:c r="M59" s="127"/>
+      <x:c r="N59" s="127"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="130"/>
+      <x:c r="B60" s="127"/>
+      <x:c r="C60" s="127"/>
+      <x:c r="D60" s="127"/>
+      <x:c r="E60" s="127"/>
+      <x:c r="F60" s="127"/>
+      <x:c r="G60" s="127"/>
+      <x:c r="H60" s="136"/>
+      <x:c r="I60" s="127"/>
+      <x:c r="J60" s="127"/>
+      <x:c r="K60" s="127"/>
+      <x:c r="L60" s="130"/>
+      <x:c r="M60" s="127"/>
+      <x:c r="N60" s="127"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="130"/>
+      <x:c r="B61" s="127"/>
+      <x:c r="C61" s="127"/>
+      <x:c r="D61" s="127"/>
+      <x:c r="E61" s="127"/>
+      <x:c r="F61" s="127"/>
+      <x:c r="G61" s="127"/>
+      <x:c r="H61" s="136"/>
+      <x:c r="I61" s="127"/>
+      <x:c r="J61" s="127"/>
+      <x:c r="K61" s="127"/>
+      <x:c r="L61" s="130"/>
+      <x:c r="M61" s="127"/>
+      <x:c r="N61" s="127"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="130"/>
+      <x:c r="B62" s="127"/>
+      <x:c r="C62" s="127"/>
+      <x:c r="D62" s="127"/>
+      <x:c r="E62" s="127"/>
+      <x:c r="F62" s="127"/>
+      <x:c r="G62" s="127"/>
+      <x:c r="H62" s="136"/>
+      <x:c r="I62" s="127"/>
+      <x:c r="J62" s="127"/>
+      <x:c r="K62" s="127"/>
+      <x:c r="L62" s="130"/>
+      <x:c r="M62" s="127"/>
+      <x:c r="N62" s="127"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="130"/>
+      <x:c r="B63" s="127"/>
+      <x:c r="C63" s="127"/>
+      <x:c r="D63" s="127"/>
+      <x:c r="E63" s="127"/>
+      <x:c r="F63" s="127"/>
+      <x:c r="G63" s="127"/>
+      <x:c r="H63" s="136"/>
+      <x:c r="I63" s="127"/>
+      <x:c r="J63" s="127"/>
+      <x:c r="K63" s="127"/>
+      <x:c r="L63" s="130"/>
+      <x:c r="M63" s="127"/>
+      <x:c r="N63" s="127"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="130"/>
+      <x:c r="B64" s="127"/>
+      <x:c r="C64" s="127"/>
+      <x:c r="D64" s="127"/>
+      <x:c r="E64" s="127"/>
+      <x:c r="F64" s="127"/>
+      <x:c r="G64" s="127"/>
+      <x:c r="H64" s="136"/>
+      <x:c r="I64" s="127"/>
+      <x:c r="J64" s="127"/>
+      <x:c r="K64" s="127"/>
+      <x:c r="L64" s="130"/>
+      <x:c r="M64" s="127"/>
+      <x:c r="N64" s="127"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="130"/>
+      <x:c r="B65" s="127"/>
+      <x:c r="C65" s="127"/>
+      <x:c r="D65" s="127"/>
+      <x:c r="E65" s="127"/>
+      <x:c r="F65" s="127"/>
+      <x:c r="G65" s="127"/>
+      <x:c r="H65" s="136"/>
+      <x:c r="I65" s="127"/>
+      <x:c r="J65" s="127"/>
+      <x:c r="K65" s="127"/>
+      <x:c r="L65" s="130"/>
+      <x:c r="M65" s="127"/>
+      <x:c r="N65" s="127"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="130"/>
+      <x:c r="B66" s="127"/>
+      <x:c r="C66" s="127"/>
+      <x:c r="D66" s="127"/>
+      <x:c r="E66" s="127"/>
+      <x:c r="F66" s="127"/>
+      <x:c r="G66" s="127"/>
+      <x:c r="H66" s="136"/>
+      <x:c r="I66" s="127"/>
+      <x:c r="J66" s="127"/>
+      <x:c r="K66" s="127"/>
+      <x:c r="L66" s="130"/>
+      <x:c r="M66" s="127"/>
+      <x:c r="N66" s="127"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="130"/>
+      <x:c r="B67" s="127"/>
+      <x:c r="C67" s="127"/>
+      <x:c r="D67" s="127"/>
+      <x:c r="E67" s="127"/>
+      <x:c r="F67" s="127"/>
+      <x:c r="G67" s="127"/>
+      <x:c r="H67" s="136"/>
+      <x:c r="I67" s="127"/>
+      <x:c r="J67" s="127"/>
+      <x:c r="K67" s="127"/>
+      <x:c r="L67" s="130"/>
+      <x:c r="M67" s="127"/>
+      <x:c r="N67" s="127"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="130"/>
+      <x:c r="B68" s="127"/>
+      <x:c r="C68" s="127"/>
+      <x:c r="D68" s="127"/>
+      <x:c r="E68" s="127"/>
+      <x:c r="F68" s="127"/>
+      <x:c r="G68" s="127"/>
+      <x:c r="H68" s="136"/>
+      <x:c r="I68" s="127"/>
+      <x:c r="J68" s="127"/>
+      <x:c r="K68" s="127"/>
+      <x:c r="L68" s="130"/>
+      <x:c r="M68" s="127"/>
+      <x:c r="N68" s="127"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="130"/>
+      <x:c r="B69" s="127"/>
+      <x:c r="C69" s="127"/>
+      <x:c r="D69" s="127"/>
+      <x:c r="E69" s="127"/>
+      <x:c r="F69" s="127"/>
+      <x:c r="G69" s="127"/>
+      <x:c r="H69" s="136"/>
+      <x:c r="I69" s="127"/>
+      <x:c r="J69" s="127"/>
+      <x:c r="K69" s="127"/>
+      <x:c r="L69" s="130"/>
+      <x:c r="M69" s="127"/>
+      <x:c r="N69" s="127"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="130"/>
+      <x:c r="B70" s="127"/>
+      <x:c r="C70" s="127"/>
+      <x:c r="D70" s="127"/>
+      <x:c r="E70" s="127"/>
+      <x:c r="F70" s="127"/>
+      <x:c r="G70" s="127"/>
+      <x:c r="H70" s="136"/>
+      <x:c r="I70" s="127"/>
+      <x:c r="J70" s="127"/>
+      <x:c r="K70" s="127"/>
+      <x:c r="L70" s="130"/>
+      <x:c r="M70" s="127"/>
+      <x:c r="N70" s="127"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="130"/>
+      <x:c r="B71" s="127"/>
+      <x:c r="C71" s="127"/>
+      <x:c r="D71" s="127"/>
+      <x:c r="E71" s="127"/>
+      <x:c r="F71" s="127"/>
+      <x:c r="G71" s="127"/>
+      <x:c r="H71" s="136"/>
+      <x:c r="I71" s="127"/>
+      <x:c r="J71" s="127"/>
+      <x:c r="K71" s="127"/>
+      <x:c r="L71" s="130"/>
+      <x:c r="M71" s="127"/>
+      <x:c r="N71" s="127"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="130"/>
+      <x:c r="B72" s="127"/>
+      <x:c r="C72" s="127"/>
+      <x:c r="D72" s="127"/>
+      <x:c r="E72" s="127"/>
+      <x:c r="F72" s="127"/>
+      <x:c r="G72" s="127"/>
+      <x:c r="H72" s="136"/>
+      <x:c r="I72" s="127"/>
+      <x:c r="J72" s="127"/>
+      <x:c r="K72" s="127"/>
+      <x:c r="L72" s="130"/>
+      <x:c r="M72" s="127"/>
+      <x:c r="N72" s="127"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="130"/>
+      <x:c r="B73" s="127"/>
+      <x:c r="C73" s="127"/>
+      <x:c r="D73" s="127"/>
+      <x:c r="E73" s="127"/>
+      <x:c r="F73" s="127"/>
+      <x:c r="G73" s="127"/>
+      <x:c r="H73" s="136"/>
+      <x:c r="I73" s="127"/>
+      <x:c r="J73" s="127"/>
+      <x:c r="K73" s="127"/>
+      <x:c r="L73" s="130"/>
+      <x:c r="M73" s="127"/>
+      <x:c r="N73" s="127"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="130"/>
+      <x:c r="B74" s="127"/>
+      <x:c r="C74" s="127"/>
+      <x:c r="D74" s="127"/>
+      <x:c r="E74" s="127"/>
+      <x:c r="F74" s="127"/>
+      <x:c r="G74" s="127"/>
+      <x:c r="H74" s="136"/>
+      <x:c r="I74" s="127"/>
+      <x:c r="J74" s="127"/>
+      <x:c r="K74" s="127"/>
+      <x:c r="L74" s="130"/>
+      <x:c r="M74" s="127"/>
+      <x:c r="N74" s="127"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="130"/>
+      <x:c r="B75" s="127"/>
+      <x:c r="C75" s="127"/>
+      <x:c r="D75" s="127"/>
+      <x:c r="E75" s="127"/>
+      <x:c r="F75" s="127"/>
+      <x:c r="G75" s="127"/>
+      <x:c r="H75" s="136"/>
+      <x:c r="I75" s="127"/>
+      <x:c r="J75" s="127"/>
+      <x:c r="K75" s="127"/>
+      <x:c r="L75" s="130"/>
+      <x:c r="M75" s="127"/>
+      <x:c r="N75" s="127"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="130"/>
+      <x:c r="B76" s="127"/>
+      <x:c r="C76" s="127"/>
+      <x:c r="D76" s="127"/>
+      <x:c r="E76" s="127"/>
+      <x:c r="F76" s="127"/>
+      <x:c r="G76" s="127"/>
+      <x:c r="H76" s="136"/>
+      <x:c r="I76" s="127"/>
+      <x:c r="J76" s="127"/>
+      <x:c r="K76" s="127"/>
+      <x:c r="L76" s="130"/>
+      <x:c r="M76" s="127"/>
+      <x:c r="N76" s="127"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="130"/>
+      <x:c r="B77" s="127"/>
+      <x:c r="C77" s="127"/>
+      <x:c r="D77" s="127"/>
+      <x:c r="E77" s="127"/>
+      <x:c r="F77" s="127"/>
+      <x:c r="G77" s="127"/>
+      <x:c r="H77" s="136"/>
+      <x:c r="I77" s="127"/>
+      <x:c r="J77" s="127"/>
+      <x:c r="K77" s="127"/>
+      <x:c r="L77" s="130"/>
+      <x:c r="M77" s="127"/>
+      <x:c r="N77" s="127"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="130"/>
+      <x:c r="B78" s="127"/>
+      <x:c r="C78" s="127"/>
+      <x:c r="D78" s="127"/>
+      <x:c r="E78" s="127"/>
+      <x:c r="F78" s="127"/>
+      <x:c r="G78" s="127"/>
+      <x:c r="H78" s="136"/>
+      <x:c r="I78" s="127"/>
+      <x:c r="J78" s="127"/>
+      <x:c r="K78" s="127"/>
+      <x:c r="L78" s="130"/>
+      <x:c r="M78" s="127"/>
+      <x:c r="N78" s="127"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="130"/>
+      <x:c r="B79" s="127"/>
+      <x:c r="C79" s="127"/>
+      <x:c r="D79" s="127"/>
+      <x:c r="E79" s="127"/>
+      <x:c r="F79" s="127"/>
+      <x:c r="G79" s="127"/>
+      <x:c r="H79" s="136"/>
+      <x:c r="I79" s="127"/>
+      <x:c r="J79" s="127"/>
+      <x:c r="K79" s="127"/>
+      <x:c r="L79" s="130"/>
+      <x:c r="M79" s="127"/>
+      <x:c r="N79" s="127"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="130"/>
+      <x:c r="B80" s="127"/>
+      <x:c r="C80" s="127"/>
+      <x:c r="D80" s="127"/>
+      <x:c r="E80" s="127"/>
+      <x:c r="F80" s="127"/>
+      <x:c r="G80" s="127"/>
+      <x:c r="H80" s="136"/>
+      <x:c r="I80" s="127"/>
+      <x:c r="J80" s="127"/>
+      <x:c r="K80" s="127"/>
+      <x:c r="L80" s="130"/>
+      <x:c r="M80" s="127"/>
+      <x:c r="N80" s="127"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="130"/>
+      <x:c r="B81" s="127"/>
+      <x:c r="C81" s="127"/>
+      <x:c r="D81" s="127"/>
+      <x:c r="E81" s="127"/>
+      <x:c r="F81" s="127"/>
+      <x:c r="G81" s="127"/>
+      <x:c r="H81" s="136"/>
+      <x:c r="I81" s="127"/>
+      <x:c r="J81" s="127"/>
+      <x:c r="K81" s="127"/>
+      <x:c r="L81" s="130"/>
+      <x:c r="M81" s="127"/>
+      <x:c r="N81" s="127"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="130"/>
+      <x:c r="B82" s="127"/>
+      <x:c r="C82" s="127"/>
+      <x:c r="D82" s="127"/>
+      <x:c r="E82" s="127"/>
+      <x:c r="F82" s="127"/>
+      <x:c r="G82" s="127"/>
+      <x:c r="H82" s="136"/>
+      <x:c r="I82" s="127"/>
+      <x:c r="J82" s="127"/>
+      <x:c r="K82" s="127"/>
+      <x:c r="L82" s="130"/>
+      <x:c r="M82" s="127"/>
+      <x:c r="N82" s="127"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="130"/>
+      <x:c r="B83" s="127"/>
+      <x:c r="C83" s="127"/>
+      <x:c r="D83" s="127"/>
+      <x:c r="E83" s="127"/>
+      <x:c r="F83" s="127"/>
+      <x:c r="G83" s="127"/>
+      <x:c r="H83" s="136"/>
+      <x:c r="I83" s="127"/>
+      <x:c r="J83" s="127"/>
+      <x:c r="K83" s="127"/>
+      <x:c r="L83" s="130"/>
+      <x:c r="M83" s="127"/>
+      <x:c r="N83" s="127"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="130"/>
+      <x:c r="B84" s="127"/>
+      <x:c r="C84" s="127"/>
+      <x:c r="D84" s="127"/>
+      <x:c r="E84" s="127"/>
+      <x:c r="F84" s="127"/>
+      <x:c r="G84" s="127"/>
+      <x:c r="H84" s="136"/>
+      <x:c r="I84" s="127"/>
+      <x:c r="J84" s="127"/>
+      <x:c r="K84" s="127"/>
+      <x:c r="L84" s="130"/>
+      <x:c r="M84" s="127"/>
+      <x:c r="N84" s="127"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="130"/>
+      <x:c r="B85" s="127"/>
+      <x:c r="C85" s="127"/>
+      <x:c r="D85" s="127"/>
+      <x:c r="E85" s="127"/>
+      <x:c r="F85" s="127"/>
+      <x:c r="G85" s="127"/>
+      <x:c r="H85" s="136"/>
+      <x:c r="I85" s="127"/>
+      <x:c r="J85" s="127"/>
+      <x:c r="K85" s="127"/>
+      <x:c r="L85" s="130"/>
+      <x:c r="M85" s="127"/>
+      <x:c r="N85" s="127"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="130"/>
+      <x:c r="B86" s="127"/>
+      <x:c r="C86" s="127"/>
+      <x:c r="D86" s="127"/>
+      <x:c r="E86" s="127"/>
+      <x:c r="F86" s="127"/>
+      <x:c r="G86" s="127"/>
+      <x:c r="H86" s="136"/>
+      <x:c r="I86" s="127"/>
+      <x:c r="J86" s="127"/>
+      <x:c r="K86" s="127"/>
+      <x:c r="L86" s="130"/>
+      <x:c r="M86" s="127"/>
+      <x:c r="N86" s="127"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="130"/>
+      <x:c r="B87" s="127"/>
+      <x:c r="C87" s="127"/>
+      <x:c r="D87" s="127"/>
+      <x:c r="E87" s="127"/>
+      <x:c r="F87" s="127"/>
+      <x:c r="G87" s="127"/>
+      <x:c r="H87" s="136"/>
+      <x:c r="I87" s="127"/>
+      <x:c r="J87" s="127"/>
+      <x:c r="K87" s="127"/>
+      <x:c r="L87" s="130"/>
+      <x:c r="M87" s="127"/>
+      <x:c r="N87" s="127"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="130"/>
+      <x:c r="B88" s="127"/>
+      <x:c r="C88" s="127"/>
+      <x:c r="D88" s="127"/>
+      <x:c r="E88" s="127"/>
+      <x:c r="F88" s="127"/>
+      <x:c r="G88" s="127"/>
+      <x:c r="H88" s="136"/>
+      <x:c r="I88" s="127"/>
+      <x:c r="J88" s="127"/>
+      <x:c r="K88" s="127"/>
+      <x:c r="L88" s="130"/>
+      <x:c r="M88" s="127"/>
+      <x:c r="N88" s="127"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="130"/>
+      <x:c r="B89" s="127"/>
+      <x:c r="C89" s="127"/>
+      <x:c r="D89" s="127"/>
+      <x:c r="E89" s="127"/>
+      <x:c r="F89" s="127"/>
+      <x:c r="G89" s="127"/>
+      <x:c r="H89" s="136"/>
+      <x:c r="I89" s="127"/>
+      <x:c r="J89" s="127"/>
+      <x:c r="K89" s="127"/>
+      <x:c r="L89" s="130"/>
+      <x:c r="M89" s="127"/>
+      <x:c r="N89" s="127"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="130"/>
+      <x:c r="B90" s="127"/>
+      <x:c r="C90" s="127"/>
+      <x:c r="D90" s="127"/>
+      <x:c r="E90" s="127"/>
+      <x:c r="F90" s="127"/>
+      <x:c r="G90" s="127"/>
+      <x:c r="H90" s="136"/>
+      <x:c r="I90" s="127"/>
+      <x:c r="J90" s="127"/>
+      <x:c r="K90" s="127"/>
+      <x:c r="L90" s="130"/>
+      <x:c r="M90" s="127"/>
+      <x:c r="N90" s="127"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="130"/>
+      <x:c r="B91" s="127"/>
+      <x:c r="C91" s="127"/>
+      <x:c r="D91" s="127"/>
+      <x:c r="E91" s="127"/>
+      <x:c r="F91" s="127"/>
+      <x:c r="G91" s="127"/>
+      <x:c r="H91" s="136"/>
+      <x:c r="I91" s="127"/>
+      <x:c r="J91" s="127"/>
+      <x:c r="K91" s="127"/>
+      <x:c r="L91" s="130"/>
+      <x:c r="M91" s="127"/>
+      <x:c r="N91" s="127"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="130"/>
+      <x:c r="B92" s="127"/>
+      <x:c r="C92" s="127"/>
+      <x:c r="D92" s="127"/>
+      <x:c r="E92" s="127"/>
+      <x:c r="F92" s="127"/>
+      <x:c r="G92" s="127"/>
+      <x:c r="H92" s="136"/>
+      <x:c r="I92" s="127"/>
+      <x:c r="J92" s="127"/>
+      <x:c r="K92" s="127"/>
+      <x:c r="L92" s="130"/>
+      <x:c r="M92" s="127"/>
+      <x:c r="N92" s="127"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="130"/>
+      <x:c r="B93" s="127"/>
+      <x:c r="C93" s="127"/>
+      <x:c r="D93" s="127"/>
+      <x:c r="E93" s="127"/>
+      <x:c r="F93" s="127"/>
+      <x:c r="G93" s="127"/>
+      <x:c r="H93" s="136"/>
+      <x:c r="I93" s="127"/>
+      <x:c r="J93" s="127"/>
+      <x:c r="K93" s="127"/>
+      <x:c r="L93" s="130"/>
+      <x:c r="M93" s="127"/>
+      <x:c r="N93" s="127"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="130"/>
+      <x:c r="B94" s="127"/>
+      <x:c r="C94" s="127"/>
+      <x:c r="D94" s="127"/>
+      <x:c r="E94" s="127"/>
+      <x:c r="F94" s="127"/>
+      <x:c r="G94" s="127"/>
+      <x:c r="H94" s="136"/>
+      <x:c r="I94" s="127"/>
+      <x:c r="J94" s="127"/>
+      <x:c r="K94" s="127"/>
+      <x:c r="L94" s="130"/>
+      <x:c r="M94" s="127"/>
+      <x:c r="N94" s="127"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="130"/>
+      <x:c r="B95" s="127"/>
+      <x:c r="C95" s="127"/>
+      <x:c r="D95" s="127"/>
+      <x:c r="E95" s="127"/>
+      <x:c r="F95" s="127"/>
+      <x:c r="G95" s="127"/>
+      <x:c r="H95" s="136"/>
+      <x:c r="I95" s="127"/>
+      <x:c r="J95" s="127"/>
+      <x:c r="K95" s="127"/>
+      <x:c r="L95" s="130"/>
+      <x:c r="M95" s="127"/>
+      <x:c r="N95" s="127"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="130"/>
+      <x:c r="B96" s="127"/>
+      <x:c r="C96" s="127"/>
+      <x:c r="D96" s="127"/>
+      <x:c r="E96" s="127"/>
+      <x:c r="F96" s="127"/>
+      <x:c r="G96" s="127"/>
+      <x:c r="H96" s="136"/>
+      <x:c r="I96" s="127"/>
+      <x:c r="J96" s="127"/>
+      <x:c r="K96" s="127"/>
+      <x:c r="L96" s="130"/>
+      <x:c r="M96" s="127"/>
+      <x:c r="N96" s="127"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="130"/>
+      <x:c r="B97" s="127"/>
+      <x:c r="C97" s="127"/>
+      <x:c r="D97" s="127"/>
+      <x:c r="E97" s="127"/>
+      <x:c r="F97" s="127"/>
+      <x:c r="G97" s="127"/>
+      <x:c r="H97" s="136"/>
+      <x:c r="I97" s="127"/>
+      <x:c r="J97" s="127"/>
+      <x:c r="K97" s="127"/>
+      <x:c r="L97" s="130"/>
+      <x:c r="M97" s="127"/>
+      <x:c r="N97" s="127"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="130"/>
+      <x:c r="B98" s="127"/>
+      <x:c r="C98" s="127"/>
+      <x:c r="D98" s="127"/>
+      <x:c r="E98" s="127"/>
+      <x:c r="F98" s="127"/>
+      <x:c r="G98" s="127"/>
+      <x:c r="H98" s="136"/>
+      <x:c r="I98" s="127"/>
+      <x:c r="J98" s="127"/>
+      <x:c r="K98" s="127"/>
+      <x:c r="L98" s="130"/>
+      <x:c r="M98" s="127"/>
+      <x:c r="N98" s="127"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="130"/>
+      <x:c r="B99" s="127"/>
+      <x:c r="C99" s="127"/>
+      <x:c r="D99" s="127"/>
+      <x:c r="E99" s="127"/>
+      <x:c r="F99" s="127"/>
+      <x:c r="G99" s="127"/>
+      <x:c r="H99" s="136"/>
+      <x:c r="I99" s="127"/>
+      <x:c r="J99" s="127"/>
+      <x:c r="K99" s="127"/>
+      <x:c r="L99" s="130"/>
+      <x:c r="M99" s="127"/>
+      <x:c r="N99" s="127"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="130"/>
+      <x:c r="B100" s="127"/>
+      <x:c r="C100" s="127"/>
+      <x:c r="D100" s="127"/>
+      <x:c r="E100" s="127"/>
+      <x:c r="F100" s="127"/>
+      <x:c r="G100" s="127"/>
+      <x:c r="H100" s="136"/>
+      <x:c r="I100" s="127"/>
+      <x:c r="J100" s="127"/>
+      <x:c r="K100" s="127"/>
+      <x:c r="L100" s="130"/>
+      <x:c r="M100" s="127"/>
+      <x:c r="N100" s="127"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="130"/>
+      <x:c r="B101" s="127"/>
+      <x:c r="C101" s="127"/>
+      <x:c r="D101" s="127"/>
+      <x:c r="E101" s="127"/>
+      <x:c r="F101" s="127"/>
+      <x:c r="G101" s="127"/>
+      <x:c r="H101" s="136"/>
+      <x:c r="I101" s="127"/>
+      <x:c r="J101" s="127"/>
+      <x:c r="K101" s="127"/>
+      <x:c r="L101" s="130"/>
+      <x:c r="M101" s="127"/>
+      <x:c r="N101" s="127"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="130"/>
+      <x:c r="B102" s="127"/>
+      <x:c r="C102" s="127"/>
+      <x:c r="D102" s="127"/>
+      <x:c r="E102" s="127"/>
+      <x:c r="F102" s="127"/>
+      <x:c r="G102" s="127"/>
+      <x:c r="H102" s="136"/>
+      <x:c r="I102" s="127"/>
+      <x:c r="J102" s="127"/>
+      <x:c r="K102" s="127"/>
+      <x:c r="L102" s="130"/>
+      <x:c r="M102" s="127"/>
+      <x:c r="N102" s="127"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="130"/>
+      <x:c r="B103" s="127"/>
+      <x:c r="C103" s="127"/>
+      <x:c r="D103" s="127"/>
+      <x:c r="E103" s="127"/>
+      <x:c r="F103" s="127"/>
+      <x:c r="G103" s="127"/>
+      <x:c r="H103" s="136"/>
+      <x:c r="I103" s="127"/>
+      <x:c r="J103" s="127"/>
+      <x:c r="K103" s="127"/>
+      <x:c r="L103" s="130"/>
+      <x:c r="M103" s="127"/>
+      <x:c r="N103" s="127"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="131"/>
+      <x:c r="B104" s="128"/>
+      <x:c r="C104" s="128"/>
+      <x:c r="D104" s="128"/>
+      <x:c r="E104" s="128"/>
+      <x:c r="F104" s="128"/>
+      <x:c r="G104" s="128"/>
+      <x:c r="H104" s="137"/>
+      <x:c r="I104" s="128"/>
+      <x:c r="J104" s="128"/>
+      <x:c r="K104" s="128"/>
+      <x:c r="L104" s="131"/>
+      <x:c r="M104" s="128"/>
+      <x:c r="N104" s="128"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:N1"/>
+    <x:mergeCell ref="A2:N2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="C5:C104">
+    <x:cfRule type="containsText" dxfId="98" priority="1" operator="containsText" text="P0"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="E5:E104">
+    <x:cfRule type="containsText" dxfId="99" priority="2" operator="containsText" text="Закрыт"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="C5:C104">
+      <x:formula1>"P0,P1,P2"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E5:E104">
+      <x:formula1>"Открыт,Сдержан,Мониторинг,Закрыт"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F5:F104">
+      <x:formula1>"Владелец,Разработчик"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc463df07bc094651"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="44" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="113" t="str">
+        <x:v>Metrics &amp; Ownership</x:v>
+      </x:c>
+      <x:c r="B1" s="113"/>
+      <x:c r="C1" s="113"/>
+      <x:c r="D1" s="113"/>
+      <x:c r="E1" s="113"/>
+      <x:c r="F1" s="113"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="116" t="str">
+        <x:v>Единые определения метрик, источники правды и ответственные. Нельзя менять формулу метрики задним числом.</x:v>
+      </x:c>
+      <x:c r="B2" s="116"/>
+      <x:c r="C2" s="116"/>
+      <x:c r="D2" s="116"/>
+      <x:c r="E2" s="116"/>
+      <x:c r="F2" s="116"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="120" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="B4" s="120" t="str">
+        <x:v>Definition</x:v>
+      </x:c>
+      <x:c r="C4" s="120" t="str">
+        <x:v>Source of truth</x:v>
+      </x:c>
+      <x:c r="D4" s="120" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="E4" s="120" t="str">
+        <x:v>Cadence</x:v>
+      </x:c>
+      <x:c r="F4" s="120" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="138" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="B5" s="138" t="str">
+        <x:v>Уникальный пользователь, открывший Mini App</x:v>
+      </x:c>
+      <x:c r="C5" s="138" t="str">
+        <x:v>analytics_events</x:v>
+      </x:c>
+      <x:c r="D5" s="138" t="str">
+        <x:v>Разработчик</x:v>
+      </x:c>
+      <x:c r="E5" s="138" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="F5" s="138" t="str">
+        <x:v>Повторный вход того же пользователя в день не считается новым</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="139" t="str">
+        <x:v>Registration</x:v>
+      </x:c>
+      <x:c r="B6" s="139" t="str">
+        <x:v>Первое успешное создание профиля</x:v>
+      </x:c>
+      <x:c r="C6" s="139" t="str">
+        <x:v>app_users</x:v>
+      </x:c>
+      <x:c r="D6" s="139" t="str">
+        <x:v>Разработчик</x:v>
+      </x:c>
+      <x:c r="E6" s="139" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="F6" s="139" t="str">
+        <x:v>Не равно простому клику по ссылке</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="139" t="str">
+        <x:v>Activation</x:v>
+      </x:c>
+      <x:c r="B7" s="139" t="str">
+        <x:v>Пользователь завершил первую реальную раздачу</x:v>
+      </x:c>
+      <x:c r="C7" s="139" t="str">
+        <x:v>hand_history</x:v>
+      </x:c>
+      <x:c r="D7" s="139" t="str">
+        <x:v>Владелец</x:v>
+      </x:c>
+      <x:c r="E7" s="139" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="F7" s="139" t="str">
+        <x:v>Тестовые боты исключаются</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="139" t="str">
+        <x:v>FTD</x:v>
+      </x:c>
+      <x:c r="B8" s="139" t="str">
+        <x:v>Первый подтверждённый cash-депозит</x:v>
+      </x:c>
+      <x:c r="C8" s="139" t="str">
+        <x:v>ledger_entries / deposits</x:v>
+      </x:c>
+      <x:c r="D8" s="139" t="str">
+        <x:v>Владелец</x:v>
+      </x:c>
+      <x:c r="E8" s="139" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="F8" s="139" t="str">
+        <x:v>Только статус paid/confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="139" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="B9" s="139" t="str">
+        <x:v>Активированный игрок вернулся на следующий календарный день</x:v>
+      </x:c>
+      <x:c r="C9" s="139" t="str">
+        <x:v>analytics_events</x:v>
+      </x:c>
+      <x:c r="D9" s="139" t="str">
+        <x:v>Разработчик</x:v>
+      </x:c>
+      <x:c r="E9" s="139" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="F9" s="139" t="str">
+        <x:v>Часовой пояс Asia/Yekaterinburg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="139" t="str">
+        <x:v>D7</x:v>
+      </x:c>
+      <x:c r="B10" s="139" t="str">
+        <x:v>Игрок проявил активность на 7-й день после активации</x:v>
+      </x:c>
+      <x:c r="C10" s="139" t="str">
+        <x:v>analytics_events</x:v>
+      </x:c>
+      <x:c r="D10" s="139" t="str">
+        <x:v>Разработчик</x:v>
+      </x:c>
+      <x:c r="E10" s="139" t="str">
+        <x:v>Weekly</x:v>
+      </x:c>
+      <x:c r="F10" s="139" t="str">
+        <x:v>Когортная метрика</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="139" t="str">
+        <x:v>Peak concurrent</x:v>
+      </x:c>
+      <x:c r="B11" s="139" t="str">
+        <x:v>Максимум одновременно сидящих живых игроков</x:v>
+      </x:c>
+      <x:c r="C11" s="139" t="str">
+        <x:v>active_table_snapshots</x:v>
+      </x:c>
+      <x:c r="D11" s="139" t="str">
+        <x:v>Владелец</x:v>
+      </x:c>
+      <x:c r="E11" s="139" t="str">
+        <x:v>Per window</x:v>
+      </x:c>
+      <x:c r="F11" s="139" t="str">
+        <x:v>Главная метрика ликвидности</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="139" t="str">
+        <x:v>Hands</x:v>
+      </x:c>
+      <x:c r="B12" s="139" t="str">
+        <x:v>Количество завершённых валидных раздач</x:v>
+      </x:c>
+      <x:c r="C12" s="139" t="str">
+        <x:v>hand_history</x:v>
+      </x:c>
+      <x:c r="D12" s="139" t="str">
+        <x:v>Разработчик</x:v>
+      </x:c>
+      <x:c r="E12" s="139" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="F12" s="139" t="str">
+        <x:v>Отменённые руки не считать</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="139" t="str">
+        <x:v>Cash rake</x:v>
+      </x:c>
+      <x:c r="B13" s="139" t="str">
+        <x:v>Сумма удержанного рейка cash-рук</x:v>
+      </x:c>
+      <x:c r="C13" s="139" t="str">
+        <x:v>ledger_entries</x:v>
+      </x:c>
+      <x:c r="D13" s="139" t="str">
+        <x:v>Владелец</x:v>
+      </x:c>
+      <x:c r="E13" s="139" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="F13" s="139" t="str">
+        <x:v>Только cash bucket</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="139" t="str">
+        <x:v>Withdrawal SLA</x:v>
+      </x:c>
+      <x:c r="B14" s="139" t="str">
+        <x:v>Часы от заявки до approve/reject</x:v>
+      </x:c>
+      <x:c r="C14" s="139" t="str">
+        <x:v>withdrawal_requests</x:v>
+      </x:c>
+      <x:c r="D14" s="139" t="str">
+        <x:v>Владелец</x:v>
+      </x:c>
+      <x:c r="E14" s="139" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="F14" s="139" t="str">
+        <x:v>Цель beta: до 24 часов</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="139" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="B15" s="139" t="str">
+        <x:v>Деньги, доступ, раскрытие карт или потеря состояния</x:v>
+      </x:c>
+      <x:c r="C15" s="139" t="str">
+        <x:v>Incident Register</x:v>
+      </x:c>
+      <x:c r="D15" s="139" t="str">
+        <x:v>Владелец</x:v>
+      </x:c>
+      <x:c r="E15" s="139" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="F15" s="139" t="str">
+        <x:v>Cash останавливается до проверки</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="139" t="str">
+        <x:v>Qualified referral</x:v>
+      </x:c>
+      <x:c r="B16" s="139" t="str">
+        <x:v>Игрок прошёл ручную проверку качества и anti-abuse</x:v>
+      </x:c>
+      <x:c r="C16" s="139" t="str">
+        <x:v>Affiliate + backend risk flags</x:v>
+      </x:c>
+      <x:c r="D16" s="139" t="str">
+        <x:v>Владелец</x:v>
+      </x:c>
+      <x:c r="E16" s="139" t="str">
+        <x:v>Weekly</x:v>
+      </x:c>
+      <x:c r="F16" s="139" t="str">
+        <x:v>Не создаёт автоматическую выплату</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="139" t="str">
+        <x:v>CAC</x:v>
+      </x:c>
+      <x:c r="B17" s="139" t="str">
+        <x:v>Расход / активированные пользователи</x:v>
+      </x:c>
+      <x:c r="C17" s="139" t="str">
+        <x:v>Acquisition</x:v>
+      </x:c>
+      <x:c r="D17" s="139" t="str">
+        <x:v>Владелец</x:v>
+      </x:c>
+      <x:c r="E17" s="139" t="str">
+        <x:v>Weekly</x:v>
+      </x:c>
+      <x:c r="F17" s="139" t="str">
+        <x:v>Всегда указывать знаменатель</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="140" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="B18" s="140" t="str">
+        <x:v>Площадка первого касания</x:v>
+      </x:c>
+      <x:c r="C18" s="140" t="str">
+        <x:v>traffic_attribution</x:v>
+      </x:c>
+      <x:c r="D18" s="140" t="str">
+        <x:v>Помощник</x:v>
+      </x:c>
+      <x:c r="E18" s="140" t="str">
+        <x:v>Per campaign</x:v>
+      </x:c>
+      <x:c r="F18" s="140" t="str">
+        <x:v>telegram, tiktok, offline и т.д.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce4c6e4b8dc6478a"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -2408,7 +6530,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="48" t="str">
-        <x:v>Beta Users</x:v>
+        <x:v>Open Beta Users</x:v>
       </x:c>
       <x:c r="B1" s="48"/>
       <x:c r="C1" s="48"/>
@@ -2427,7 +6549,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="49" t="str">
-        <x:v>Кто приглашён, откуда пришёл, прошёл ли активацию и когда играл в последний раз.</x:v>
+        <x:v>Все игроки открытого теста: источник, активация, денежный статус и последняя активность. Доступ к боту не ограничивается списком.</x:v>
       </x:c>
       <x:c r="B2" s="49"/>
       <x:c r="C2" s="49"/>
@@ -4231,7 +8353,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75ac71509ce44acd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R183cc2a1b3d74fb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5874,7 +9996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdffcef423b72481a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff7605d0e3f0446b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7821,7 +11943,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bf857d46ed44380"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c3970795982421e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9458,7 +13580,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d73424d7db94602"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6024189c65b48ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12514,7 +16636,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1685dd903b44d19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6edef8d6ec8f4e16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12543,7 +16665,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="48" t="str">
-        <x:v>Affiliate Beta</x:v>
+        <x:v>Affiliate Pilot</x:v>
       </x:c>
       <x:c r="B1" s="48"/>
       <x:c r="C1" s="48"/>
@@ -12563,7 +16685,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="49" t="str">
-        <x:v>Закрытый ручной пилот. Никаких публичных обещаний RevShare/CPA до утверждения экономики и anti-abuse.</x:v>
+        <x:v>Ручной пилот качества трафика. Выплата только после anti-abuse review; публичные CPA/RevShare не обещаются.</x:v>
       </x:c>
       <x:c r="B2" s="49"/>
       <x:c r="C2" s="49"/>
@@ -14472,7 +18594,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ffcb2f311114f38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09c61bb97d4448ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14519,7 +18641,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="49" t="str">
-        <x:v>Контент-план канала @weezpoker и внешних размещений. Один материал — одна строка.</x:v>
+        <x:v>План и факт публикаций @weezpoker. Каждая внешняя ссылка получает отдельный attribution code.</x:v>
       </x:c>
       <x:c r="B2" s="49"/>
       <x:c r="C2" s="49"/>
@@ -16323,7 +20445,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e5f0fd648e1455a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77d83d1b29bf4304"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18262,7 +22384,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb88850b98a641ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68fb7e5d41a44b5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>